--- a/Abgabe_Quellen.xlsx
+++ b/Abgabe_Quellen.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Metadaten" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Abgabequellen'!$A$1:$R$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nicht_gezaehlt'!$A$1:$R$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Abgabequellen'!$A$1:$R$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nicht_gezaehlt'!$A$1:$R$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Seitenbudget'!$A$1:$C$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadaten'!$A$1:$B$6</definedName>
   </definedNames>
@@ -443,13 +443,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -738,57 +738,45 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>baudson2021wasdenken</t>
+          <t>preckel2013hochbegabung</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>115--128</t>
+          <t>15--47</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Baudson, Tanja Gabriele</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
-        </is>
-      </c>
+          <t>Preckel, Franzis; Baudson, Tanja Gabriele</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Was Menschen über (Hoch-)Begabung und (Hoch-)Begabte denken: Individuelle und soziokulturelle Perspektiven</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch Begabung</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>115–129</t>
-        </is>
-      </c>
+          <t>Hochbegabung: Erkennen, Verstehen, Fördern</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>15 S. (S. 115–129). Seitenspanne von Inti verifiziert (KERNLITERATUR\_INTI.md, Fragen 1, 3, 5); der Scan umfasst die Fliesstext-Seiten 115–128 plus die erste Literaturseite 129. Volltext via OCR (source.pdf, komprimiert 6.7 MB) vorliegend. Gliederung: (1) Begriffliche Abgrenzungen, (2) Erkennen mit IQ-Kritik und Lehrkrafturteil ($\rho = .50$), (3) Hochbegabungs- konzeptionen (Disharmonie-Stereotyp, Cultural Mismatch, Minoritätenstress, Cass-Stufenmodell), (4) Folgerungen für globalisierte Gesellschaft. Schlüsselbeleg für FW1 (Sprache als Identifikationsbarriere, S. 120), FW3 (kultursensible Begabungsdiagnostik, S. 125) und BW4 (Inklusionsdebatte vergisst Begabung, S. 119). Vollständige verified\_quotes.md Status 4 vorliegend.</t>
+          <t>Kap. 1 (Erkennen, Begabung als Potenzial): S. 11–30 (20 S., reduziert).</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -820,45 +808,57 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>preckel2013hochbegabung</t>
+          <t>gauckreimann2021psychdiagnostik</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15--47</t>
+          <t>239--249</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Preckel, Franzis; Baudson, Tanja Gabriele</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>Gauck, Letizia; Reimann, Giselle</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Hochbegabung: Erkennen, Verstehen, Fördern</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>Psychologische Diagnostik in der Begabungs- und Begabtenförderung</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>239–251</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Kap. 1 (Erkennen, Begabung als Potenzial): S. 11–30 (20 S., reduziert).</t>
+          <t>ca. 13 S. Vier-Schritte-Prozess; Deckeneffekt; Aisha-/Lea-Vignetten (deutschsprachiger Fallbeleg für Unteridentifikation). Frage 1 Kernliteratur; in Frage 5 nicht gezählt, da in der Frage-5-Tabelle nicht als eingereicht und nicht als Stützliteratur markiert.</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -890,57 +890,53 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>muelleroppliger2021begabungsmodelle</t>
+          <t>haag2018leistungsstanddiagnostik</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>204--219</t>
+          <t>153--165, 187--188</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Victor</t>
+          <t>Haag, Nicole; Heppt, Birgit; Schipolowski, Stefan</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+          <t>Maehler, Débora B.; Shajek, Alexandra; Brinkmann, Heinz Ulrich</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Begabungsmodelle: Entwicklungslinien und Positionen zur Erfassung des Phänomens der Hochbegabung</t>
+          <t>Leistungsstanddiagnostik</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Handbuch Begabung</t>
+          <t>Diagnostik bei Migrantinnen und Migranten: Ein Handbuch</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>204–222</t>
+          <t>153–165, 187–188</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>16 S. (S. 204–219, ohne Literaturverzeichnis). Dynamisch-mehrdimensionale Begabungsmodelle: Renzulli (Drei-Ringe), Mönks (Triadisches Interdependenzmodell), Münchner Hochbegabungsmodell (Heller/Perleth), Aktiotop (Ziegler), DMGT (Gagné). Begabung als entwicklungsoffenes Potenzial; Differenzierung Potenzial/Performanz.</t>
-        </is>
-      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -972,57 +968,57 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>muelleroppliger2021paeddiagnostik</t>
+          <t>kellerkoller2025hellekoepfe</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>224--235</t>
+          <t>76--78</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Salomé</t>
+          <t>Keller-Koller, Isabella</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+          <t>Huser, Joëlle</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Pädagogische Diagnostik: Potenzialerfassung und Förderdiagnostik</t>
+          <t>Helle Köpfe mit Migrationshintergrund: warum sie oft unerkannt bleiben</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Handbuch Begabung</t>
+          <t>Lichtblick für helle Köpfe: Ein Wegweiser zur Erkennung und Förderung von hohen Fähigkeiten bei Kindern und Jugendlichen auf allen Schulstufen</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>224–238</t>
+          <t>76–78</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>ca. 15 S. Phasenmodell vermuten/wahrnehmen/erkennen; Meeraugenprinzip; Förder- vs. Statusdiagnostik.</t>
+          <t>3 S. (S. 76–78). Aus der 3. Aufl. 2025 (Ausgabe 2021) des Handbuchs; Kapitel neu gegenüber der 1. Aufl. 2004 (vgl. Lehrmittelverlag Zürich: "3. Auflage 2025, Ausgabe 2021"). BibKey zu Konsistenzgründen beibehalten.</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1050,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>gauckreimann2021psychdiagnostik</t>
+          <t>baumschader2021twice</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>239--249</t>
+          <t>588--598</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
@@ -1067,7 +1063,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Gauck, Letizia; Reimann, Giselle</t>
+          <t>Baum, Susan; Schader, Robin</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1082,7 +1078,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Psychologische Diagnostik in der Begabungs- und Begabtenförderung</t>
+          <t>\enquoteTwice Exceptionality – in zweifacher Hinsicht aussergewöhnlich: Geschichte, Charakteristika und Möglichkeiten erfolgreichen Lernens</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1092,19 +1088,19 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>239–251</t>
+          <t>588–600</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>ca. 13 S. Vier-Schritte-Prozess; Deckeneffekt; Aisha-/Lea-Vignetten (deutschsprachiger Fallbeleg für Unteridentifikation).</t>
+          <t>13 S. Gesamtumfang; Frage 1 zählt S. 588–598 (11 S.); Frage 2 und Frage 3 Stützliteratur, nicht gezählt. Schlussbeitrag im Teil VIII \enquoteDysfunktionale Begabungsentwicklung des Handbuchs Begabung. Historische Entwicklung des 2e-Konzepts, Charakteristika und Lernbedingungen. Volltext verfügbar via teil8\_dysfunktionale\_begabungsentwicklung.md in baumschader2021twice/.</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1136,53 +1132,61 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>haag2018leistungsstanddiagnostik</t>
+          <t>koop2025herkunft</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>153--165, 187--188</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Haag, Nicole; Heppt, Birgit; Schipolowski, Stefan</t>
+          <t>Koop, Christine</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Maehler, Débora B.; Shajek, Alexandra; Brinkmann, Heinz Ulrich</t>
+          <t>Pauly, Claudia</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Leistungsstanddiagnostik</t>
+          <t>Die Herkunft entscheidet zu oft über die Chancen</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Diagnostik bei Migrantinnen und Migranten: Ein Handbuch</t>
+          <t>Was ist fair? Begabungsgerechtigkeit auf dem Prüfstand</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153–165, 187–188</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
+          <t>64–69</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>10.25656/01:33972</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>6 S. (S. 64–69). Erg\"anzende Transferliteratur, Frage 1 und Frage 4. Diagnostikfairness: auch nonverbale Tests sind nicht automatisch gerecht. F\"orderung als diagnostische Gelegenheit lesen (S. 68: \"15–20% ausw\"ahlen, F\"orderung liefert diagnostische Erkenntnisse\"). Verifiziert via pdf\_extract.py. Open Access via pedocs.</t>
+        </is>
+      </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1214,27 +1218,23 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>kellerkoller2025hellekoepfe</t>
+          <t>stern2025intelligenz</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>76--78</t>
+          <t>15--18</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Keller-Koller, Isabella</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Huser, Joëlle</t>
-        </is>
-      </c>
+          <t>Stern, Elsbeth</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2025</t>
@@ -1242,29 +1242,21 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Helle Köpfe mit Migrationshintergrund: warum sie oft unerkannt bleiben</t>
+          <t>Die Intelligenz kann sich im Schulalter noch verändern</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Lichtblick für helle Köpfe: Ein Wegweiser zur Erkennung und Förderung von hohen Fähigkeiten bei Kindern und Jugendlichen auf allen Schulstufen</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>76–78</t>
-        </is>
-      </c>
+          <t>Bildung Schweiz: Zeitschrift des LCH</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3 S. (S. 76–78). Aus der 3. Aufl. 2025 (Ausgabe 2021) des Handbuchs; Kapitel neu gegenüber der 1. Aufl. 2004 (vgl. Lehrmittelverlag Zürich: "3. Auflage 2025, Ausgabe 2021"). BibKey zu Konsistenzgründen beibehalten.</t>
-        </is>
-      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1296,57 +1288,45 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>baumschader2021twice</t>
+          <t>webb2020doppeldiagnosen</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>588--598</t>
+          <t>87--94</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Baum, Susan; Schader, Robin</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
-        </is>
-      </c>
+          <t>Webb, James T.; Amend, Edward R.; Beljan, Paul; Webb, Nadia E.; Kuzujanakis, Marianne; Olenchak, F. Richard; Goerss, Jean</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>\enquoteTwice Exceptionality – in zweifacher Hinsicht aussergewöhnlich: Geschichte, Charakteristika und Möglichkeiten erfolgreichen Lernens</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch Begabung</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>588–600</t>
-        </is>
-      </c>
+          <t>Doppeldiagnosen und Fehldiagnosen bei Hochbegabung: Ein Ratgeber für Fachpersonen und Betroffene</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>13 S. (S. 588–600). Schlussbeitrag im Teil VIII \enquoteDysfunktionale Begabungsentwicklung des Handbuchs Begabung. Historische Entwicklung des 2e-Konzepts, Charakteristika und Lernbedingungen. Volltext verfügbar via teil8\_dysfunktionale\_begabungsentwicklung.md in baumschader2021twice/.</t>
+          <t>Lokal verfügbare Foto-Auszüge (komprimiert): (a) Kap. 2 \enquoteFehldiagnosen und Doppeldiagnosen bei hochbegabten Kindern und Erwachsenen, S. 87–94 (8 S.) – siehe Literatur/webb2020doppeldiagnosen/kap02\_fehldiagnosen\_doppeldiagnosen\_s087-094.pdf; (b) Kap. 12 \enquoteDer diagnostische Prozess, S. 351–376 (26 S.) – siehe Literatur/webb2020doppeldiagnosen/kap12\_diagnostischer\_prozess\_s351-376.pdf. Zusammen ca. 34 S. Volltext.</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1378,61 +1358,57 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>koop2025herkunft</t>
+          <t>stahl2021mbet</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>252--258</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Koop, Christine</t>
+          <t>Stahl, Johanna</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Pauly, Claudia</t>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Die Herkunft entscheidet zu oft über die Chancen</t>
+          <t>Das multidimensionale Begabungs-Entwicklungs-Tool (mBET) als Instrument multifunktionaler Förderdiagnostik</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Was ist fair? Begabungsgerechtigkeit auf dem Prüfstand</t>
+          <t>Handbuch Begabung</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64–69</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>10.25656/01:33972</t>
-        </is>
-      </c>
+          <t>252–258</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>6 S. (S. 64–69). Erg\"anzende Transferliteratur, Frage 1 und Frage 4. Diagnostikfairness: auch nonverbale Tests sind nicht automatisch gerecht. F\"orderung als diagnostische Gelegenheit lesen (S. 68: \"15–20% ausw\"ahlen, F\"orderung liefert diagnostische Erkenntnisse\"). Verifiziert via pdf\_extract.py. Open Access via pedocs.</t>
+          <t>ca. 7 S. mBET des özbf: Multiperspektivität (LP/Eltern/Lernende).</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1464,57 +1440,69 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>stern2025intelligenz</t>
+          <t>warneckehauke2020bildungsgerechtigkeit</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15--18</t>
+          <t>241--252</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Stern, Elsbeth</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+          <t>Warnecke, Sabine; Hauke, Robert</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Fischer, Christian; Fischer-Ontrup, Christiane; Käpnick, Friedhelm; Neuber, Nils; Solzbacher, Claudia; Zwitserlood, Pienie</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Die Intelligenz kann sich im Schulalter noch verändern</t>
+          <t>Stärkung der Bildungsgerechtigkeit bei Underachievement, Migration und Hochbegabung: Drei Beispiele aus der Förderpraxis</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Bildung Schweiz: Zeitschrift des LCH</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>Begabungsförderung, Leistungsentwicklung, Bildungsgerechtigkeit – für alle! II. Beiträge aus der Begabungsförderung</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>241–252</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>12 S. (S. 241–252). Frage 1 zählt S. 241–252; Frage 2 Stützliteratur S. 247–252, nicht gezählt. Praxis- und Gerechtigkeitsbezug. Drei Beispiele aus der Förderpraxis: Underachievement, Migration und Hochbegabung gemeinsam adressiert. Beziehung, Geduld, positive Verstärkung, Offenheit für individuelle Unterschiede, Passung zu besonderen Interessen. Cited content: S. 247–252.</t>
+        </is>
+      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Frage 2 (FW, MW/KS: Barrieren)</t>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1534,53 +1522,45 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>saegesserwyss2022grafinkrahmenmodell</t>
+          <t>kellerkoller2011erkennen</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1--19</t>
+          <t>1--2</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>S\"agesser Wyss, Judith; Sahli Lozano, Caroline; Eckhart, Michael</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Vetter, Martin; Wuttig, Bettina; Spahn, Lea; G\"ohle, Henrik</t>
-        </is>
-      </c>
+          <t>Keller-Koller, Isabella</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Grafomotorik und schulische Inklusion: Entwicklung und Anwendung eines Rahmenmodells</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Gesellschaft und Diversit\"at: Beitr\"age aus Sicht von Motologie und Psychomotorik zu bewegungs- und wahrnehmungsbezogener Forschung, Profession und Praxis</t>
-        </is>
-      </c>
+          <t>Begabte mit Migrationshintergrund – Erkennen und Fördern</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Preprint via ResearchGate, P\"adagogische Hochschule Bern. Verlag und Druckseiten vor Abgabe verifizieren. Kerngehalt f\"ur Frage 2: Arbeitsged\"achtnis als Flaschenhals (S. 1 f.); fachdidaktische Wirksamkeit interessengebundener Schreibanl\"asse (S. 6); GRAFOS-Verortung im inklusiven Rahmen (S. 7, 11). Bezug zu Frage 5: vier Ebenen multiprofessioneller Kooperation nach Wocken (S. 9 f.).</t>
-        </is>
-      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.lissa-preis.ch</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1612,57 +1592,53 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>nottbusch2017graphomotorik</t>
+          <t>saegesserwyss2022grafinkrahmenmodell</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>125--138</t>
+          <t>1--2, 6--11</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Nottbusch, Guido</t>
+          <t>S\"agesser Wyss, Judith; Sahli Lozano, Caroline; Eckhart, Michael</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Becker-Mrotzek, Michael; Grabowski, Joachim; Steinhoff, Torsten</t>
+          <t>Vetter, Martin; Wuttig, Bettina; Spahn, Lea; G\"ohle, Henrik</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Graphomotorik</t>
+          <t>Grafomotorik und schulische Inklusion: Entwicklung und Anwendung eines Rahmenmodells</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Forschungshandbuch empirische Schreibdidaktik</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>125–138</t>
-        </is>
-      </c>
+          <t>Gesellschaft und Diversit\"at: Beitr\"age aus Sicht von Motologie und Psychomotorik zu bewegungs- und wahrnehmungsbezogener Forschung, Profession und Praxis</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>14 S. Peer-reviewed Kapitel. Teil B \enquoteEntwicklung der Schreibkompetenz des Forschungshandbuchs. Zentrale Forschungssynthese zur Graphomotorik (Chunking, Automatisierung, Alterstrajektorien).</t>
+          <t>Preprint via ResearchGate, P\"adagogische Hochschule Bern. Verlag und Druckseiten vor Abgabe verifizieren. Frage 2 zählt S. 1–2, 6–11 (8 S.). Kerngehalt: Arbeitsged\"achtnis als Flaschenhals (S. 1 f.); fachdidaktische Wirksamkeit interessengebundener Schreibanl\"asse (S. 6); GRAFOS-Verortung im inklusiven Rahmen (S. 7, 11). Bezug zu Frage 5: vier Ebenen multiprofessioneller Kooperation nach Wocken (S. 9 f.).</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1694,53 +1670,57 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>hurschler2020handschriftbeurteilung</t>
+          <t>nottbusch2017graphomotorik</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1--26</t>
+          <t>128--136</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Hurschler Lichtsteiner, Sibylle</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+          <t>Nottbusch, Guido</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Becker-Mrotzek, Michael; Grabowski, Joachim; Steinhoff, Torsten</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Differenzierende Beurteilung der Handschrift: Ein Bestandteil der Schreibförderung</t>
+          <t>Graphomotorik</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>leseforum.ch: Online-Plattform für Literalität</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>Forschungshandbuch empirische Schreibdidaktik</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>125–138</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.leseforum.ch/sysModules/obxLeseforum/Artikel/711/2020_3_de_hurschler.pdf</t>
-        </is>
-      </c>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>26 S. Schweizer Lehrplan-21-Bezug; Leserlichkeit + Geläufigkeit als Beurteilungskriterien. Zentrale Grundlage für diagnostische Schreib-Förderung in FW2.</t>
+          <t>14 S. Gesamtumfang; Frage 2 zählt S. 128–136 (9 S.). Peer-reviewed Kapitel. Teil B \enquoteEntwicklung der Schreibkompetenz des Forschungshandbuchs. Zentrale Forschungssynthese zur Graphomotorik (Chunking, Automatisierung, Alterstrajektorien).</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1772,45 +1752,53 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>gold2018lesenkannmanlernen</t>
+          <t>hurschler2020handschriftbeurteilung</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>62, 67--70, 88</t>
+          <t>1--24</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Gold, Andreas</t>
+          <t>Hurschler Lichtsteiner, Sibylle</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Lesen kann man lernen: Wie man die Lesekompetenz f\"ordern kann</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>Differenzierende Beurteilung der Handschrift: Ein Bestandteil der Schreibförderung</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>leseforum.ch: Online-Plattform für Literalität</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.leseforum.ch/sysModules/obxLeseforum/Artikel/711/2020_3_de_hurschler.pdf</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>S. 62–66 (Schwache Leser: Graphem-Phonem-Zuordnung, Sichtwortschatz, weiterf\"uhrendes Lesen) und Kap. 5, S. 67–88 (Lesefl\"ussigkeit als Br\"ucke, drei Niveaus mit Frustrationsniveau unter 40 WPM auf S. 70, Lautleseverfahren auf S. 88). Zusammen 27 S. Inti gelesen, im Repo als PDF abgelegt.</t>
+          <t>26 S. Gesamtumfang; Frage 2 zählt S. 1–24 (24 S.). Schweizer Lehrplan-21-Bezug; Leserlichkeit + Geläufigkeit als Beurteilungskriterien. Zentrale Grundlage für diagnostische Schreib-Förderung in FW2.</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1842,31 +1830,31 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>lehwald2017motivation</t>
+          <t>gold2018lesenkannmanlernen</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>70--72, 84--89</t>
+          <t>50--53, 62, 67--88</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Lehwald, Gerhard</t>
+          <t>Gold, Andreas</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Motivation trifft Begabung: Begabte Kinder und Jugendliche verstehen und gezielt fördern</t>
+          <t>Lesen kann man lernen: Wie man die Lesekompetenz f\"ordern kann</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
@@ -1875,12 +1863,12 @@
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Kernreferenzen: (a) S. 57–63 = Fall Pawel, hochbegabter Underachiever, dokumentierte Parallele zu S.; (b) S. 70–72 = Sechsstufige Stufenfolge ins Underachievement (Abb. 2-5); (c) S. 84–89 = Flow als empirisch st\"arkster Begabungspr\"adiktor; (d) S. 151–158 = F\"orderlogik (Differenzierung, Compacting, Enrichment, Akzeleration), Frage 4 Kernliteratur. Bewusst nicht im Korpus: HST-P/FES/BVE (S. 107–134) wegen Sprachbarriere bei S.; Triadisches Modell (S. 65–69) wegen Redundanz.</t>
+          <t>Frage 2 zählt S. 50–53, 62, 67–88 mit 27 S. nach inklusiver Seitenzählung. Schwerpunkt: Vorläufer- und Wortlesekompetenzen, Graphem-Phonem-Zuordnung, Sichtwortschatz, Leseflüssigkeit als Brücke, Frustrationsniveau unter 40 WPM und Lautleseverfahren. Im Repo als PDF abgelegt.</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1912,57 +1900,45 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>greiten2021underachievement</t>
+          <t>lehwald2017motivation</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>546--555</t>
+          <t>70--72, 84--89</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Greiten, Silvia</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
-        </is>
-      </c>
+          <t>Lehwald, Gerhard</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Underachievement: Begriff und Konzept</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch Begabung</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>546–555</t>
-        </is>
-      </c>
+          <t>Motivation trifft Begabung: Begabte Kinder und Jugendliche verstehen und gezielt fördern</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>10 S. (S. 546–555). Kanonische deutschsprachige Definition von Underachievement. Diskrepanzdefinition, Ursachencluster (psychosozial, personenbezogen, unterrichtlich, systemisch), Diagnostik und Förderung. Teil VIII \enquoteDysfunktionale Begabungsentwicklung des Handbuchs Begabung.</t>
+          <t>Kernreferenzen: (a) S. 57–63 = Fall Pawel, hochbegabter Underachiever, Frage 3 Stützliteratur, nicht gezählt; (b) S. 70–72 = Sechsstufige Stufenfolge ins Underachievement (Abb. 2-5); (c) S. 84–89 = Flow als empirisch st\"arkster Begabungspr\"adiktor; (d) S. 151–158 = F\"orderlogik (Differenzierung, Compacting, Enrichment, Akzeleration), Frage 4 Kernliteratur. Bewusst nicht im Korpus: HST-P/FES/BVE (S. 107–134) wegen Sprachbarriere bei S.; Triadisches Modell (S. 65–69) wegen Redundanz.</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -1994,57 +1970,57 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>warneckehauke2020bildungsgerechtigkeit</t>
+          <t>greiten2021underachievement</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>241--252</t>
+          <t>546--553</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Warnecke, Sabine; Hauke, Robert</t>
+          <t>Greiten, Silvia</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Fischer, Christian; Fischer-Ontrup, Christiane; Käpnick, Friedhelm; Neuber, Nils; Solzbacher, Claudia; Zwitserlood, Pienie</t>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Stärkung der Bildungsgerechtigkeit bei Underachievement, Migration und Hochbegabung: Drei Beispiele aus der Förderpraxis</t>
+          <t>Underachievement: Begriff und Konzept</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Begabungsförderung, Leistungsentwicklung, Bildungsgerechtigkeit – für alle! II. Beiträge aus der Begabungsförderung</t>
+          <t>Handbuch Begabung</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>241–252</t>
+          <t>546–555</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>12 S. (S. 241–252). Frage 2 Kernliteratur: Praxis- und Gerechtigkeitsbezug. Drei Beispiele aus der Förderpraxis: Underachievement, Migration und Hochbegabung gemeinsam adressiert. Beziehung, Geduld, positive Verstärkung, Offenheit für individuelle Unterschiede, Passung zu besonderen Interessen. Cited content: S. 247–252.</t>
+          <t>10 S. Gesamtumfang; Frage 2 zählt S. 546–553 (8 S.). Kanonische deutschsprachige Definition von Underachievement. Diskrepanzdefinition, Ursachencluster (psychosozial, personenbezogen, unterrichtlich, systemisch), Diagnostik und Förderung. Teil VIII \enquoteDysfunktionale Begabungsentwicklung des Handbuchs Begabung.</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2076,61 +2052,57 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>kuhl2019diversitaet</t>
+          <t>grossrieder2010anerkennung</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35--48</t>
+          <t>88--94</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Kuhl, Julius; Hofmann, Franz</t>
+          <t>Grossrieder, Ivo</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Reintjes, Christian; Kunze, Ingrid; Ossowski, Ekkehard</t>
+          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Diversität und Persönlichkeit: Begabungsentfaltung im Kontext der pädagogischen Beziehung</t>
+          <t>Gleiches und Unterschiedliches anerkennen</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Begabungsförderung und Professionalisierung: Befunde, Perspektiven, Herausforderungen</t>
+          <t>Alle gleich – alle unterschiedlich: Zum Umgang mit Heterogenität in Schule und Unterricht</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35–59</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>10.25656/01:17448</t>
-        </is>
-      </c>
+          <t>87–94</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>25 S. (S. 35–59). Verifiziert via Klinkhardt Open-Access-PDF (urn:nbn:de:0111-pedocs-174484); Käpnick-Beitrag schliesst auf S. 60 an.</t>
+          <t>7 S. (S. 88–94). Frage 3 Kernliteratur. Fliesstext-Spanne von Inti verifiziert (KERNLITERATUR\_INTI.md, Frage 3); gesamter Beitrag geht mit Literatur bis S. 95. Kapitelbeitrag im Buholzer/Kummer-Wyss-Sammelband.</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2162,57 +2134,57 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>grossrieder2010anerkennung</t>
+          <t>baudson2021wasdenken</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88--94</t>
+          <t>115--129</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Grossrieder, Ivo</t>
+          <t>Baudson, Tanja Gabriele</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Gleiches und Unterschiedliches anerkennen</t>
+          <t>Was Menschen über (Hoch-)Begabung und (Hoch-)Begabte denken: Individuelle und soziokulturelle Perspektiven</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Alle gleich – alle unterschiedlich: Zum Umgang mit Heterogenität in Schule und Unterricht</t>
+          <t>Handbuch Begabung</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>87–94</t>
+          <t>115–129</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>7 S. (S. 87–94). Fliesstext-Spanne von Inti verifiziert (KERNLITERATUR\_INTI.md, Frage 3); gesamter Beitrag geht mit Literatur bis S. 95. Kapitelbeitrag im Buholzer/Kummer-Wyss-Sammelband.</t>
+          <t>15 S. Gesamtumfang; Frage 3 zählt S. 115–129 (15 S.); Frage 1 und Frage 4 Stützliteratur, nicht gezählt. Seitenspanne von Inti verifiziert (KERNLITERATUR\_INTI.md, Fragen 1, 3, 5); der Scan umfasst die Fliesstext-Seiten 115–128 plus die erste Literaturseite 129. Volltext via OCR (source.pdf, komprimiert 6.7 MB) vorliegend. Gliederung: (1) Begriffliche Abgrenzungen, (2) Erkennen mit IQ-Kritik und Lehrkrafturteil ($\rho = .50$), (3) Hochbegabungs- konzeptionen (Disharmonie-Stereotyp, Cultural Mismatch, Minoritätenstress, Cass-Stufenmodell), (4) Folgerungen für globalisierte Gesellschaft. Schlüsselbeleg für FW1 (Sprache als Identifikationsbarriere, S. 120), FW3 (kultursensible Begabungsdiagnostik, S. 125) und BW4 (Inklusionsdebatte vergisst Begabung, S. 119). Vollständige verified\_quotes.md Status 4 vorliegend.</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2244,61 +2216,57 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>kesselshannover2015gleichaltrige</t>
+          <t>kuhl2021begabungbildungbeziehung</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>185--201</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Kessels, Ursula; Hannover, Bettina</t>
+          <t>Kuhl, Julius</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Wild, Elke; Möller, Jens</t>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Gleichaltrige</t>
+          <t>Begabung, Bildung und Beziehung aus persönlichkeitspsychologischer Sicht</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Pädagogische Psychologie</t>
+          <t>Handbuch Begabung</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>283–301</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-642-41291-2_12</t>
-        </is>
-      </c>
+          <t>185–203</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>19 S. (S. 283–301). Kapitel 12 in Wild/Möller (Hrsg.) 2015 (2. Aufl., nicht 3. Aufl. 2020). Konzeptioneller Beitrag zu Peers, Beliebtheit, Freundschaft, Homophilie, Bullying, sozialer Identität. Frage 3-Standardreferenz. Achtung Auflagen-Verifikation vor Abgabe.</t>
+          <t>19 S. Gesamtumfang; Frage 3 zählt S. 185–201 (17 S.). Persönlichkeitspsychologische Sicht auf Begabung, Bildung und Beziehung.</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2330,57 +2298,57 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>behrensen2019inklusive</t>
+          <t>wagener2021bfhemmendfoerdernd</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>86--98</t>
+          <t>418--424</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Behrensen, Birgit</t>
+          <t>Wagener, Gundula</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Reintjes, Christian; Kunze, Ingrid; Ossowski, Ekkehard</t>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Inklusive Begabungsförderung – eine Antwort auf Bildungsherausforderungen in Zeiten von Fluchtmigration</t>
+          <t>Begabungsfördernde und hemmende Wirkungsmechanismen im Klassenkontext</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Begabungsförderung und Professionalisierung: Befunde, Perspektiven, Herausforderungen</t>
+          <t>Handbuch Begabung</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>86–98</t>
+          <t>418–426</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>13 S.</t>
+          <t>9 S. Gesamtumfang; Frage 3 zählt S. 418–424 (7 S.); Frage 5 Stützliteratur S. 418–424, nicht gezählt. Teil V \enquoteBegabender Unterricht. Systemtheoretischer Rahmen mit Aktiotop und ökologischem Begabungsmodell (S. 418\psq); \enquoteDie Klasse macht den Unterschied (Schweitz 2003, S. 420); Bildungskapital-Typologie nach Ziegler/Stöger 2013 mit fünf Kategorien (S. 420\psq); Zimmer/Toma 2003 und Opdenakker/Van Damme 2001 zu sozioökonomisch differenzierten Effekten (S. 421); Peer-Mechanismen Big-Fish-Little-Pond, Acting White, Signaltheorie, Ansteckungstheorie (S. 421\psq) – relevant für begabte Migrantenkinder zwischen Peer-Kulturen; Pygmalion-Effekt auf Klassenebene (S. 423\psq); mehrstufige Zuständigkeitsaussage Lehrperson/Schulleitung/Bildungspolitik (S. 425); Quality Teaching als Effective+Good Teaching (Berliner 2005, S. 425\psq).</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2412,25 +2380,25 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>booth2019index</t>
+          <t>behrensen2019inklusive</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>101--125</t>
+          <t>86--98</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Booth, Tony; Ainscow, Mel</t>
+          <t>Behrensen, Birgit</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Achermann, Bruno; Amirpur, Donja; Braunsteiner, Maria-Luise; Demo, Heidrun; Plate, Elisabeth; Platte, Andrea</t>
+          <t>Reintjes, Christian; Kunze, Ingrid; Ossowski, Ekkehard</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2440,21 +2408,29 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Index für Inklusion: Ein Leitfaden für Schulentwicklung</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>Inklusive Begabungsförderung – eine Antwort auf Bildungsherausforderungen in Zeiten von Fluchtmigration</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Begabungsförderung und Professionalisierung: Befunde, Perspektiven, Herausforderungen</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>86–98</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Dimensionen A–C: ca. 90 S. (verteilt auf Fr. 3 und 4)</t>
+          <t>13 S. (S. 86–98). Frage 3 Kernliteratur.</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2486,45 +2462,61 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>tschoppgruetterbuholzer2022intergruppenkontakt</t>
+          <t>kuhl2019diversitaet</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>35--40</t>
+          <t>35--54</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Tschopp, Cécile; Grütter, Jeanine; Buholzer, Alois</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>Kuhl, Julius; Hofmann, Franz</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Reintjes, Christian; Kunze, Ingrid; Ossowski, Ekkehard</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Soziale Teilhabe durch Intergruppenkontakt: Wie Freundschaften von Kindern mit heilpädagogischem Förderbedarf unterstützt werden können</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>Diversität und Persönlichkeit: Begabungsentfaltung im Kontext der pädagogischen Beziehung</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Begabungsförderung und Professionalisierung: Befunde, Perspektiven, Herausforderungen</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>35–41</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr"/>
+          <t>35–59</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>10.25656/01:17448</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>7 S. (S. 35–41). Schweizer Forschungsbeitrag zum Intergruppenkontakt-Effekt für Freundschaften bei SPF-Kindern; Allport + PHLU-Programm. verified\_quotes.md vorliegend.</t>
+          <t>25 S. Gesamtumfang; Frage 3 zählt S. 35–54 (20 S.). Verifiziert via Klinkhardt Open-Access-PDF (urn:nbn:de:0111-pedocs-174484); Käpnick-Beitrag schliesst auf S. 60 an.</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2541,12 +2533,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>gezaehlte Stuetzliteratur</t>
+          <t>Kernliteratur</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2556,57 +2548,49 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>kappus2010migration</t>
+          <t>boosnuenning2022interethnisch</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>67--70</t>
+          <t>51--65</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Kappus, Elke-Nicole</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
+          <t>Boos-Nünning, Ursula</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Umgang mit migrationsbedingter Heterogenität</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>Alle gleich – alle unterschiedlich: Zum Umgang mit Heterogenität in Schule und Unterricht</t>
-        </is>
-      </c>
+          <t>Interethnische Freundschaften unter den Bedingungen sozialräumlicher und institutioneller Segregation</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>63–77</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr"/>
+          <t>51–71</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>10.11576/pflb-5882</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>15 S. (S. 63–77). Volltext (Foto-Scan, komprimiert) liegt vor unter Literatur/kappus2010migration/source.pdf (5,0 MB). Inhaltsverzeichnis- Position bestätigt via Buholzer-Sammelband (Universitätsbibliothek Basel, IDSBB 005018146): Kappus-Beitrag steht in Teil I \enquoteErscheinungsweisen von Heterogenität.</t>
+          <t>21 S. Gesamtumfang; Frage 3 zählt S. 51–65 mit 15 S. nach inklusiver Seitenzählung. Strukturanalyse zu Bedingungen interethnischer Freundschaften (Wohnort, Schule, Institutionen). verified\_quotes.md vorliegend.</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2623,12 +2607,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>gezaehlte Stuetzliteratur</t>
+          <t>Kernliteratur</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2638,45 +2622,61 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>lehwald2017motivation</t>
+          <t>kesselshannover2015gleichaltrige</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>57--63</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Lehwald, Gerhard</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
+          <t>Kessels, Ursula; Hannover, Bettina</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Wild, Elke; Möller, Jens</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Motivation trifft Begabung: Begabte Kinder und Jugendliche verstehen und gezielt fördern</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+          <t>Gleichaltrige</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Pädagogische Psychologie</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>283–301</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-642-41291-2_12</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Kernreferenzen: (a) S. 57–63 = Fall Pawel, hochbegabter Underachiever, dokumentierte Parallele zu S.; (b) S. 70–72 = Sechsstufige Stufenfolge ins Underachievement (Abb. 2-5); (c) S. 84–89 = Flow als empirisch st\"arkster Begabungspr\"adiktor; (d) S. 151–158 = F\"orderlogik (Differenzierung, Compacting, Enrichment, Akzeleration), Frage 4 Kernliteratur. Bewusst nicht im Korpus: HST-P/FES/BVE (S. 107–134) wegen Sprachbarriere bei S.; Triadisches Modell (S. 65–69) wegen Redundanz.</t>
+          <t>19 S. Gesamtumfang; Frage 3 zählt S. 288 (1 S.). Kapitel 12 in Wild/Möller (Hrsg.) 2015 (2. Aufl., nicht 3. Aufl. 2020). Konzeptioneller Beitrag zu Peers, Beliebtheit, Freundschaft, Homophilie, Bullying, sozialer Identität. Frage 3-Standardreferenz. Achtung Auflagen-Verifikation vor Abgabe.</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2693,12 +2693,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>gezaehlte Stuetzliteratur</t>
+          <t>Kernliteratur</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2708,45 +2708,45 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>gysinscherzinger2022freundschaftenwertvoll</t>
+          <t>stamm2014mirage</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>10--11</t>
+          <t>102--115</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Gysin, Stefanie; Scherzinger, Marion</t>
+          <t>Stamm, Margrit; Leumann, Seraina; Kost, Jakob</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Freundschaften machen das Leben wertvoll</t>
+          <t>Erfolgreiche Migranten: Ihr Ausbildungs- und Berufserfolg im Schweizer Berufsbildungssystem</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>8–12</t>
-        </is>
-      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>5 S. (S. 8–12). Schweizer Beitrag zur Bedeutung von Freundschaften für Wohlbefinden. Volltext-Auszug in Literatur/gysinscherzinger2022freundschaftenwertvoll/source.pdf (Seiten 8–12 aus dem Heft extrahiert).</t>
+          <t>Frage 3 zählt S. 102–115 (14 S.) gemäss Abgabe-Tabelle. Forschungsbericht zum Ausbildungs- und Berufserfolg erfolgreicher Migrantinnen und Migranten im Schweizer Berufsbildungssystem.</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>gezaehlte Stuetzliteratur</t>
+          <t>Kernliteratur</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2778,71 +2778,67 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>baumert2022freundschaftwerte</t>
+          <t>tschoppgruetterbuholzer2022intergruppenkontakt</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>40--46</t>
+          <t>35--40</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Baumert, Britta</t>
+          <t>Tschopp, Cécile; Grütter, Jeanine; Buholzer, Alois</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>\enquoteMan kann nicht leben, wenn man keine Freunde hat: Wertezuschreibungen Jugendlicher mit und ohne Fluchterfahrung im Themenbereich Freundschaft</t>
+          <t>Soziale Teilhabe durch Intergruppenkontakt: Wie Freundschaften von Kindern mit heilpädagogischem Förderbedarf unterstützt werden können</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>36–50</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>10.11576/pflb-5878</t>
-        </is>
-      </c>
+          <t>35–41</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>15 S. Empirische Studie zu Freundschaftswerten bei Jugendlichen mit/ohne Fluchterfahrung. Direkter Bezug zu Frage 3 (Migration + Peer-Beziehungen). verified\_quotes.md vorliegend (Status 4).</t>
+          <t>7 S. Gesamtumfang; Frage 3 zählt S. 35–40 (6 S.). Schweizer Forschungsbeitrag zum Intergruppenkontakt-Effekt für Freundschaften bei SPF-Kindern; Allport + PHLU-Programm. verified\_quotes.md vorliegend.</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Frage 3 (FW, PB: Beziehung)</t>
+          <t>Frage 4 (BW, DG/PV: Setting)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>K</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>gezaehlte Stuetzliteratur</t>
+          <t>Kernliteratur</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2852,61 +2848,57 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>evers2025stress</t>
+          <t>buholzerkummerwyss2010reaktionen</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>22--23</t>
+          <t>78--85</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Evers, Wiebke</t>
+          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Pauly, Claudia</t>
+          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Stress als Dämpfer für die kognitive Entwicklung und die Entfaltung von Begabung</t>
+          <t>Zur Einführung: Reaktionen auf Heterogenität in Schule und Unterricht</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Was ist fair? Begabungsgerechtigkeit auf dem Prüfstand</t>
+          <t>Alle gleich – alle unterschiedlich: Zum Umgang mit Heterogenität in Schule und Unterricht</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>21–27</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>10.25656/01:33972</t>
-        </is>
-      </c>
+          <t>78–86</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>7 S. (S. 21–27). Erg\"anzende Transferliteratur, Frage 3. Dauerstress beeintr\"achtigt Lernen, Selbstregulation, Ged\"achtnis und Probleml\"osen. Verifiziert via pdf\_extract.py. Open Access via pedocs.</t>
+          <t>Frage 4 zählt S. 78–85 (8 S.) gemäss Abgabe-Tabelle. Einführender Beitrag zu Reaktionen auf Heterogenität in Schule und Unterricht.</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -2938,20 +2930,20 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>reisrenzullimueller2021sem</t>
+          <t>muelleroppliger2021plurale</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>333--347</t>
+          <t>32--42</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Reis, Sally M.; Renzulli, Joseph S.; Müller-Oppliger, Victor</t>
+          <t>Müller-Oppliger, Victor</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2966,7 +2958,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Das Schoolwide Enrichment Model (SEM): Vier Jahrzehnte Forschung zur Entwicklung von Talenten und kreativer Produktivität</t>
+          <t>Plurale Gesellschaft, Inklusion und Bildungsgerechtigkeit</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2976,19 +2968,19 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>333–347</t>
+          <t>32–45</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>15 S. (S. 333–347). SEM-Hauptbeitrag im Handbuch Begabung, Teil IV \enquoteBegabende Schule. Drei-Ringe-Konzept als anti-essenzialistische Basis (S. 334\psq); RIS mit alternativen Identifikationspfaden für die 50 % nicht durch Standardtests Erkannten (S. 337); Enrichment Triad mit Typ I/II/III (S. 338\psq); Drehtürmodell (S. 342) und Schlüsselsatz \enquoteBegabung ist kein schulpsychologischer Fall; Curriculum Compacting (S. 343\psq); Schweizer SEM-Praxis an PH FHNW seit 2003 (S. 344\psq); Längsschnittstudien Delcourt 1993, Hébert 1993, Westberg, Renzulli/Reis 2014 (S. 346\psq). Achtung: Im bisherigen Manuskript fälschlich unter dem Citekey \textttrenzullireis2021rls zitiert – jener verweist auf den anderen Beitrag der beiden Autor:innen zum \enquoteRenzulli-Lernsystem (S. 444–454).</t>
+          <t>14 S. Gesamtumfang; Frage 4 zählt S. 32–42 (11 S.); Frage 5 Stützliteratur S. 32–45, nicht gezählt.</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3020,57 +3012,57 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>buholzerkummerwyss2010heterogenitaet</t>
+          <t>muelleroppliger2021begabungsmodelle</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>7--12</t>
+          <t>204--219</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
+          <t>Müller-Oppliger, Victor</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Heterogenität als Herausforderung für Schule und Unterricht</t>
+          <t>Begabungsmodelle: Entwicklungslinien und Positionen zur Erfassung des Phänomens der Hochbegabung</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Alle gleich – alle unterschiedlich: Zum Umgang mit Heterogenität in Schule und Unterricht</t>
+          <t>Handbuch Begabung</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>7–12</t>
+          <t>204–222</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>6 S. (S. 7–12). Eröffnungsbeitrag des Sammelbands. Buchprüfung 2026-05-01 am PDF-Auszug (Literatur/buholzer2010allegleich/source\_s7-12.pdf): Homogenitätslogik des Bildungssystems (S. 9), TIMSS-Befund (55 % der Lehrkräfte: Leistungsheterogenität als Berufserschwernis, S. 8), Polarisierungen wie \enquotenormale Kinder und Migrantenkinder (S. 9), Pädagogik der Vielfalt (S. 8), alternative Beurteilungsformen (S. 10) sind tatsächlich auf S. 7–12 belegt. Frage 4 Kernliteratur. Vormaliger Citekey \textttbuholzerkummerwyss2010einfuehrung ersetzt; Titel an Originalkapitelüberschrift angeglichen.</t>
+          <t>16 S. (S. 204–219, ohne Literaturverzeichnis). Frage 4 Kernliteratur; Frage 1 Stützliteratur, nicht gezählt. Dynamisch- mehrdimensionale Begabungsmodelle: Renzulli (Drei-Ringe), Mönks (Triadisches Interdependenzmodell), Münchner Hochbegabungsmodell (Heller/Perleth), Aktiotop (Ziegler), DMGT (Gagné). Begabung als entwicklungsoffenes Potenzial; Differenzierung Potenzial/Performanz.</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3102,20 +3094,20 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>weigand2021separativ</t>
+          <t>reisrenzullimueller2021sem</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>290--298</t>
+          <t>333--345</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Weigand, Gabriele; Kaiser, Michaela</t>
+          <t>Reis, Sally M.; Renzulli, Joseph S.; Müller-Oppliger, Victor</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3130,7 +3122,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Separativ oder integrativ? Inklusive Begabungs- und Begabtenförderung</t>
+          <t>Das Schoolwide Enrichment Model (SEM): Vier Jahrzehnte Forschung zur Entwicklung von Talenten und kreativer Produktivität</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3140,19 +3132,19 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>290–298</t>
+          <t>333–347</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>9 S. (S. 290–298). Frage 4 Kernliteratur. Cheflektorat 2026-05-01: Seitenangabe von zuvor 290–301 auf 290–298 korrigiert (Originalumfang des argumentativen Kapitelteils; das Folgekapitel Anderegg/Wilhelm beginnt im Sammelband nach S. 298).</t>
+          <t>15 S. Gesamtumfang; Frage 4 zählt S. 333–345 (13 S.); Frage 5 Stützliteratur, nicht gezählt. SEM-Hauptbeitrag im Handbuch Begabung, Teil IV \enquoteBegabende Schule. Drei-Ringe-Konzept als anti-essenzialistische Basis (S. 334\psq); RIS mit alternativen Identifikationspfaden für die 50 % nicht durch Standardtests Erkannten (S. 337); Enrichment Triad mit Typ I/II/III (S. 338\psq); Drehtürmodell (S. 342) und Schlüsselsatz \enquoteBegabung ist kein schulpsychologischer Fall; Curriculum Compacting (S. 343\psq); Schweizer SEM-Praxis an PH FHNW seit 2003 (S. 344\psq); Längsschnittstudien Delcourt 1993, Hébert 1993, Westberg, Renzulli/Reis 2014 (S. 346\psq). Achtung: Im bisherigen Manuskript fälschlich unter dem Citekey \textttrenzullireis2021rls zitiert – jener verweist auf den anderen Beitrag der beiden Autor:innen zum \enquoteRenzulli-Lernsystem (S. 444–454).</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3184,12 +3176,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>sedmak2021bildungsgerechtigkeit</t>
+          <t>muelleroppliger2021paeddiagnostik</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>65--76</t>
+          <t>224--235</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -3197,7 +3189,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Sedmak, Clemens; Kapferer, Elisabeth</t>
+          <t>Müller-Oppliger, Salomé</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3212,7 +3204,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Begabtenförderung und Bildungsgerechtigkeit</t>
+          <t>Pädagogische Diagnostik: Potenzialerfassung und Förderdiagnostik</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3222,19 +3214,19 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>65–76</t>
+          <t>224–238</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>12 S. (S. 65–76). Frage 4 im 500-S.-Korpus.</t>
+          <t>15 S. Gesamtumfang; Frage 4 zählt S. 224–235 (12 S.); Frage 1 und Frage 5 Stützliteratur, nicht gezählt. Phasenmodell vermuten/wahrnehmen/erkennen; Meeraugenprinzip; Förder- vs. Statusdiagnostik.</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3266,20 +3258,20 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>muelleroppliger2021plurale</t>
+          <t>weigand2021separativ</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>32--45</t>
+          <t>290--298</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Victor</t>
+          <t>Weigand, Gabriele; Kaiser, Michaela</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3294,7 +3286,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Plurale Gesellschaft, Inklusion und Bildungsgerechtigkeit</t>
+          <t>Separativ oder integrativ? Inklusive Begabungs- und Begabtenförderung</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3304,19 +3296,19 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>32–45</t>
+          <t>290–298</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>14 S. (S. 32–45). Frage 4 im 500-S.-Korpus.</t>
+          <t>9 S. (S. 290–298). Frage 4 Kernliteratur; Frage 5 Stützliteratur, nicht gezählt. Cheflektorat 2026-05-01: Seitenangabe von zuvor 290–301 auf 290–298 korrigiert (Originalumfang des argumentativen Kapitelteils; das Folgekapitel Anderegg/Wilhelm beginnt im Sammelband nach S. 298).</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3348,20 +3340,20 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>preckel2021tad</t>
+          <t>muelleroppliger2021adaptive</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>274--289</t>
+          <t>374--385</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Preckel, Franzis</t>
+          <t>Müller-Oppliger, Victor</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3376,7 +3368,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Das TAD-Framework: Ein Rahmenmodell zur Beschreibung von Begabung und Leistung unter einer Talententwicklungsperspektive</t>
+          <t>Adaptive Lernarchitekturen: Begabungs- und Begabtenförderung innerhalb der Lerngemeinschaft</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3386,19 +3378,19 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>274–303</t>
+          <t>374–389</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>ca. 30 S. Vier Phasen Talententwicklung: Potenzial, Kompetenz, Expertise, aussergewöhnliche Leistung; Weiterentwicklung des Mega-Modells (Subotnik et al. 2011).</t>
+          <t>16 S. Gesamtumfang; Frage 4 zählt S. 374–385 (12 S.); Frage 5 Stützliteratur S. 384–385, nicht gezählt. Teil V \enquoteBegabender Unterricht. Definition adaptiver Lernarchitektur als Anpassung der Wissensvermittlung an Wissensstand, Lernpräferenzen und Möglichkeiten der Lernenden (S. 374\psq); empirische Wirksamkeit über alle ethnischen und sozioökonomischen Gruppen, Walberg-Metaanalyse 38 Studien/7200 Lernende (S. 375\psq); Ermöglichungsdidaktik nach Arnold/Schön 2019 (S. 377); vier konstituierende Merkmale (S. 378\psq); Hochbegabung weit mehr als fachliche Exzellenz, vier Bildungsdimensionen Begabung+soziales Kapital/Leadership/Verantwortung/Ethik (S. 380\psq); Lernberatung nach Shulman 2006 mit Knowing What/How/Why (S. 386\psq); erweiterte Leistungsbeurteilung mit Portfolio/Logbuch/Lernjournal (S. 387\psq); Schluss \enquoteanders als die anderen löst sich auf, denn alle sind anders (S. 388\psq). Achtung: Im PDF-Dateinamen und in einer früheren Manuskript-Version fälschlich als \enquoteS. 274–285 bzw. \enquoteS. 274–385 annotiert; auf S. 274–303 steht im Sammelband Preckels TAD-Beitrag.</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3472,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3512,57 +3504,45 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>grossenbacher2014integrative</t>
+          <t>lehwald2017motivation</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>317--325</t>
+          <t>151--158</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Grossenbacher, Silvia; Tettenborn, Annette</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Stamm, Margrit</t>
-        </is>
-      </c>
+          <t>Lehwald, Gerhard</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Talent und Begabung in der Volksschule der deutschsprachigen Schweiz</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch Talententwicklung: Theorien, Methoden und Praxis in Psychologie und Pädagogik</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>317–325</t>
-        </is>
-      </c>
+          <t>Motivation trifft Begabung: Begabte Kinder und Jugendliche verstehen und gezielt fördern</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>Frage 4 Kernliteratur: S. 317–325 (9 S.). Schweizer Volksschulkontext, integrative Begabungs- und Begabtenf\"orderung als Auftrag der Volksschule, Massnahmenrepertoire (Differenzierung, Compacting, Enrichment, Akzeleration, Pullout, regionale Angebote), Kooperation Regelunterricht und Heilp\"adagogik, Schulentwicklung. Aus demselben Sammelband: \citestamm2014handbuch. Verifiziert via DNB (idn=1045975508) und lokaler Foto-Scan.</t>
+          <t>Kernreferenzen: (a) S. 57–63 = Fall Pawel, hochbegabter Underachiever, Frage 3 Stützliteratur, nicht gezählt; (b) S. 70–72 = Sechsstufige Stufenfolge ins Underachievement (Abb. 2-5); (c) S. 84–89 = Flow als empirisch st\"arkster Begabungspr\"adiktor; (d) S. 151–158 = F\"orderlogik (Differenzierung, Compacting, Enrichment, Akzeleration), Frage 4 Kernliteratur. Bewusst nicht im Korpus: HST-P/FES/BVE (S. 107–134) wegen Sprachbarriere bei S.; Triadisches Modell (S. 65–69) wegen Redundanz.</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3594,31 +3574,31 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>lehwald2017motivation</t>
+          <t>hoyer2013begabung</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>151--158</t>
+          <t>94--99</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Lehwald, Gerhard</t>
+          <t>Hoyer, Timo; Weigand, Gabriele; Müller-Oppliger, Victor</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Motivation trifft Begabung: Begabte Kinder und Jugendliche verstehen und gezielt fördern</t>
+          <t>Begabung: Eine Einführung</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
@@ -3627,12 +3607,12 @@
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Kernreferenzen: (a) S. 57–63 = Fall Pawel, hochbegabter Underachiever, dokumentierte Parallele zu S.; (b) S. 70–72 = Sechsstufige Stufenfolge ins Underachievement (Abb. 2-5); (c) S. 84–89 = Flow als empirisch st\"arkster Begabungspr\"adiktor; (d) S. 151–158 = F\"orderlogik (Differenzierung, Compacting, Enrichment, Akzeleration), Frage 4 Kernliteratur. Bewusst nicht im Korpus: HST-P/FES/BVE (S. 107–134) wegen Sprachbarriere bei S.; Triadisches Modell (S. 65–69) wegen Redundanz.</t>
+          <t>Vorgaenger-/Schwesterpublikation zu Handbuch Begabung 2021. Frage 4 zählt S. 94–99 (6 S.). Kap. 5.1 Konzepte/Modelle (Gardner, Multiple Intelligenzen); Kap. 6.6 Turning Point: Das ``Three Ring Concept''; Kap. 7.1 Das ``Schoolwide Enrichment Model'' als Choreografie inklusiver Begabungs- und Begabtenfoerderung.</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3664,45 +3644,57 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>hoyer2013begabung</t>
+          <t>sedmak2021bildungsgerechtigkeit</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>94--99</t>
+          <t>65--75</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Hoyer, Timo; Weigand, Gabriele; Müller-Oppliger, Victor</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
+          <t>Sedmak, Clemens; Kapferer, Elisabeth</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Begabung: Eine Einführung</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>Begabtenförderung und Bildungsgerechtigkeit</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>65–76</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Vorgaenger-/Schwesterpublikation zu Handbuch Begabung 2021. Kap. 5.1 Konzepte/Modelle (Gardner, Multiple Intelligenzen); Kap. 6.6 Turning Point: Das ``Three Ring Concept''; Kap. 7.1 Das ``Schoolwide Enrichment Model'' als Choreografie inklusiver Begabungs- und Begabtenfoerderung.</t>
+          <t>12 S. Gesamtumfang; Frage 4 zählt S. 65–75 (11 S.); Frage 5 Stützliteratur S. 65–75, nicht gezählt.</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3734,57 +3726,57 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>baudson2021wasdenken</t>
+          <t>grossenbacher2014integrative</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>317--325</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Baudson, Tanja Gabriele</t>
+          <t>Grossenbacher, Silvia; Tettenborn, Annette</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+          <t>Stamm, Margrit</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Was Menschen über (Hoch-)Begabung und (Hoch-)Begabte denken: Individuelle und soziokulturelle Perspektiven</t>
+          <t>Talent und Begabung in der Volksschule der deutschsprachigen Schweiz</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Handbuch Begabung</t>
+          <t>Handbuch Talententwicklung: Theorien, Methoden und Praxis in Psychologie und Pädagogik</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>115–129</t>
+          <t>317–325</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>15 S. (S. 115–129). Seitenspanne von Inti verifiziert (KERNLITERATUR\_INTI.md, Fragen 1, 3, 5); der Scan umfasst die Fliesstext-Seiten 115–128 plus die erste Literaturseite 129. Volltext via OCR (source.pdf, komprimiert 6.7 MB) vorliegend. Gliederung: (1) Begriffliche Abgrenzungen, (2) Erkennen mit IQ-Kritik und Lehrkrafturteil ($\rho = .50$), (3) Hochbegabungs- konzeptionen (Disharmonie-Stereotyp, Cultural Mismatch, Minoritätenstress, Cass-Stufenmodell), (4) Folgerungen für globalisierte Gesellschaft. Schlüsselbeleg für FW1 (Sprache als Identifikationsbarriere, S. 120), FW3 (kultursensible Begabungsdiagnostik, S. 125) und BW4 (Inklusionsdebatte vergisst Begabung, S. 119). Vollständige verified\_quotes.md Status 4 vorliegend.</t>
+          <t>Frage 4 Kernliteratur: S. 317–325 (9 S.). Schweizer Volksschulkontext, integrative Begabungs- und Begabtenf\"orderung als Auftrag der Volksschule, Massnahmenrepertoire (Differenzierung, Compacting, Enrichment, Akzeleration, Pullout, regionale Angebote), Kooperation Regelunterricht und Heilp\"adagogik, Schulentwicklung. Aus demselben Sammelband: \citestamm2014handbuch. Verifiziert via DNB (idn=1045975508) und lokaler Foto-Scan.</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3816,20 +3808,20 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>muelleroppliger2021paeddiagnostik</t>
+          <t>weigand2021person</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>224--238</t>
+          <t>46--59</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Salomé</t>
+          <t>Weigand, Gabriele</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3844,7 +3836,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Pädagogische Diagnostik: Potenzialerfassung und Förderdiagnostik</t>
+          <t>Begabung, Bildung und Person</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -3854,19 +3846,19 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>224–238</t>
+          <t>46–63</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>ca. 15 S. Phasenmodell vermuten/wahrnehmen/erkennen; Meeraugenprinzip; Förder- vs. Statusdiagnostik.</t>
+          <t>18 S. Gesamtumfang; Frage 5 zählt S. 46–59 (14 S.); Frage 4 Stützliteratur, nicht gezählt. Philosophisch-pädagogisches Fundament: konstitutive, kritisch-konstruktive und regulative Funktion des Personenprinzips.</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3898,20 +3890,20 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>weigand2021person</t>
+          <t>horvath2021elite</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>46--59</t>
+          <t>77--87</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Weigand, Gabriele</t>
+          <t>Horvath, Kenneth</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3926,7 +3918,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Begabung, Bildung und Person</t>
+          <t>Elite, Begabung und soziale Ungleichheit: Ungelöste Gerechtigkeitsfragen</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -3936,19 +3928,19 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>46–63</t>
+          <t>77–87</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>ca. 18 S. Philosophisch-päd. Fundament: konstitutive/kritisch-konstruktive/regulative Funktion des Personenprinzips.</t>
+          <t>Frage 5 Kernliteratur: S. 77–87 (11 S.); Frage 4 Stützliteratur, nicht gezählt. Von Inti verifiziert (KERNLITERATUR\_INTI.md, Fragen 1, 4, 5). Meritokratische Illusion, Pygmalion-Effekt, Migrationshintergrund als verwobene Kategorie.</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -3980,25 +3972,25 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>horvath2021elite</t>
+          <t>muellerboeschschaffnermenn2021udl</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>77--87</t>
+          <t>94--116</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Horvath, Kenneth</t>
+          <t>M\"uller B\"osch, Cornelia; Schaffner Menn, Anita</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+          <t>Kunz, Andr\'e; Luder, Reto; M\"uller B\"osch, Cornelia</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -4008,29 +4000,29 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Elite, Begabung und soziale Ungleichheit: Ungelöste Gerechtigkeitsfragen</t>
+          <t>Inklusiver Unterricht: Lernen in einem universellen Design am gemeinsamen Gegenstand</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Handbuch Begabung</t>
+          <t>Inklusive P\"adagogik und Didaktik</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>77–87</t>
+          <t>93–119</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>11 S. (S. 77–87). Von Inti verifiziert (KERNLITERATUR\_INTI.md, Fragen 1, 4, 5). Meritokratische Illusion, Pygmalion-Effekt, Migrationshintergrund als verwobene Kategorie.</t>
+          <t>27 S. Gesamtumfang; Frage 5 zählt S. 94–116 (23 S.). hep Verlag, 2. Aufl. 2021. Verbindung Feusers \enquoteLernen in Kooperation am gemeinsamen Gegenstand mit dem Universal Design for Learning (UDL). 3P-Modell (Markowetz): Pr\"asenz, Partizipation, P\"adagogik. Erweitertes didaktisches Dreieck (Reusser/Pauli). Frage 4- und Frage 5-relevant.</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -4062,57 +4054,61 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>reisrenzullimueller2021sem</t>
+          <t>macha2019gender</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>333--342</t>
+          <t>160--171</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Reis, Sally M.; Renzulli, Joseph S.; Müller-Oppliger, Victor</t>
+          <t>Macha, Hildegard</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+          <t>Reintjes, Christian; Kunze, Ingrid; Ossowski, Ekkehard</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Das Schoolwide Enrichment Model (SEM): Vier Jahrzehnte Forschung zur Entwicklung von Talenten und kreativer Produktivität</t>
+          <t>Gender- und diversitätssensible Begabungsförderung und Professionalisierung</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Handbuch Begabung</t>
+          <t>Begabungsförderung und Professionalisierung: Befunde, Perspektiven, Herausforderungen</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>333–347</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr"/>
+          <t>160–173</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>10.25656/01:17448</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>15 S. (S. 333–347). SEM-Hauptbeitrag im Handbuch Begabung, Teil IV \enquoteBegabende Schule. Drei-Ringe-Konzept als anti-essenzialistische Basis (S. 334\psq); RIS mit alternativen Identifikationspfaden für die 50 % nicht durch Standardtests Erkannten (S. 337); Enrichment Triad mit Typ I/II/III (S. 338\psq); Drehtürmodell (S. 342) und Schlüsselsatz \enquoteBegabung ist kein schulpsychologischer Fall; Curriculum Compacting (S. 343\psq); Schweizer SEM-Praxis an PH FHNW seit 2003 (S. 344\psq); Längsschnittstudien Delcourt 1993, Hébert 1993, Westberg, Renzulli/Reis 2014 (S. 346\psq). Achtung: Im bisherigen Manuskript fälschlich unter dem Citekey \textttrenzullireis2021rls zitiert – jener verweist auf den anderen Beitrag der beiden Autor:innen zum \enquoteRenzulli-Lernsystem (S. 444–454).</t>
+          <t>Frage 5 Kernliteratur: S. 160–171 (12 S.). Verifiziert via Klinkhardt Open-Access-PDF (urn:nbn:de:0111-pedocs-174484); Fischer-Beitrag schliesst auf S. 174 an.</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -4185,12 +4181,12 @@
       <c r="P47" s="2" t="inlineStr"/>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>19 S. (S. 461–479). Zeitschrift f\"ur P\"adagogik 66(4). Drei Formen der Kooperation: Austausch, arbeitsteilige Kooperation, Kokonstruktion. Modell mit Rahmenbedingungen, sozialen Vorbedingungen (Zielinterdependenz, Vertrauen, Egalit\"at, Reziprozit\"at, Deprivatisierung), Handlungen, proximalen und distalen Folgen. Frage 5 zentrale Theoriequelle. Eine ZB-Auszugsversion (4 S.) liegt zus\"atzlich als zb\_wirkmodell\_konstruktive\_kooperation.pdf im selben Ordner.</t>
+          <t>19 S. Gesamtumfang; Frage 5 zählt S. 463–467 und S. 469–472 (9 S.). Zeitschrift f\"ur P\"adagogik 66(4). Drei Formen der Kooperation: Austausch, arbeitsteilige Kooperation, Kokonstruktion. Modell mit Rahmenbedingungen, sozialen Vorbedingungen (Zielinterdependenz, Vertrauen, Egalit\"at, Reziprozit\"at, Deprivatisierung), Handlungen, proximalen und distalen Folgen. Frage 5 zentrale Theoriequelle. Eine ZB-Auszugsversion (4 S.) liegt zus\"atzlich als zb\_wirkmodell\_konstruktive\_kooperation.pdf im selben Ordner.</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -4267,12 +4263,12 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>11 S. (S. 348–358). Teil IV des Handbuchs Begabung. Internationale Vergleichsperspektive: PISA/TIMSS-Stagnation Deutschlands seit 2000 (S. 348); Lehrerausbildungsschwächen und Internationale Vorbilder Jyväskylä/Amsterdam (S. 349\psq); UDL und adaptive Lehrkompetenz (Brühwiler 2014, S. 350\psq); Cognitive Apprenticeship Model (S. 351\psq); Growth Mindset (Dweck 2008, S. 352\psq); Schulen als professionelle Lerngemeinschaften (S. 354\psq); kontinuierliche konzeptionelle Zusammenarbeit Lehrperson/SHP (S. 355); Wrap-Around-Service-Schools Kanada/Finnland (S. 355\psq); \textbfCard/Giuliano (2015/2016) Verdreifachung der hispanischen/afroamerikanischen Identifikation durch flächendeckendes Screening (S. 355\psq) – empirischer Schlüsselbefund für Frage 5; Schluss: multiperspektivischer Ansatz unter Berücksichtigung sozioökonomischer Verhältnisse (S. 356).</t>
+          <t>11 S. Gesamtumfang; Frage 5 zählt S. 348–356 (9 S.). Teil IV des Handbuchs Begabung. Internationale Vergleichsperspektive: PISA/TIMSS-Stagnation Deutschlands seit 2000 (S. 348); Lehrerausbildungsschwächen und Internationale Vorbilder Jyväskylä/Amsterdam (S. 349\psq); UDL und adaptive Lehrkompetenz (Brühwiler 2014, S. 350\psq); Cognitive Apprenticeship Model (S. 351\psq); Growth Mindset (Dweck 2008, S. 352\psq); Schulen als professionelle Lerngemeinschaften (S. 354\psq); kontinuierliche konzeptionelle Zusammenarbeit Lehrperson/SHP (S. 355); Wrap-Around-Service-Schools Kanada/Finnland (S. 355\psq); \textbfCard/Giuliano (2015/2016) Verdreifachung der hispanischen/afroamerikanischen Identifikation durch flächendeckendes Screening (S. 355\psq) – empirischer Schlüsselbefund für Frage 5; Schluss: multiperspektivischer Ansatz unter Berücksichtigung sozioökonomischer Verhältnisse (S. 356).</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -4304,61 +4300,57 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>ziesenitz2024routenplan</t>
+          <t>widmerwolf2018multiprofessionell</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>75--82</t>
+          <t>299--303, 308--309</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Ziesenitz, Anna Katharina</t>
+          <t>Widmer-Wolf, Patrik</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Breyel, Sabine; Evers, Wiebke; Koop, Christine; Lotze, Miriam</t>
+          <t>Sturm, Tanja; Wagner-Willi, Monika</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Underachievement: Ein Routenplan für den Dschungel</t>
+          <t>Kooperation in multiprofessionellen Teams an inklusiven Schulen</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Underachievement in der Schule. Potenziale sehen, Entwicklung begleiten</t>
+          <t>Handbuch schulische Inklusion</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>75–82</t>
-        </is>
-      </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>10.25656/01:32095</t>
-        </is>
-      </c>
+          <t>299–313</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>8 S. (S. 75–82). Erg\"anzende Transferliteratur, Frage 5. Stufenlogik: Beobachten, Dokumentieren, Diagnostik, F\"orderplan im Team. Operationalisierung der SHP-Trias. Verifiziert via pdf\_extract.py. Open Access via pedocs.</t>
+          <t>15 S. Gesamtumfang; Frage 5 zählt S. 299–303 und S. 308–309 (7 S.). Voraussetzungsgef\"uge multiprofessioneller Zusammenarbeit; Autonomie und Kooperation als zirkul\"are Aspekte; vier Berufsfelder (sonderp\"adagogische F\"orderung, Schulsozialarbeit, DaZ, Logop\"adie). Theoriebez\"uge: Werning/L\"oser 2010, Fussangel/Gr\"asel 2010/2011. Frage 5 zentrale Quelle.</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -4390,53 +4382,45 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>widmerwolf2018multiprofessionell</t>
+          <t>kosoroklabhart2021voneltern</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>299--303, 308--309</t>
+          <t>14--15, 38--39</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Widmer-Wolf, Patrik</t>
+          <t>Košorok Labhart, Carmen; Luginbühl, Dora; Schöllhorn, Angelika</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Kooperation in multiprofessionellen Teams an inklusiven Schulen</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch schulische Inklusion</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>299–313</t>
-        </is>
-      </c>
+          <t>Von Eltern mit Migrationshintergrund lernen: Denkanstösse für die kultursensible Praxis in Spielgruppe, Kita und Schule</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>15 S. (S. 299–313). Voraussetzungsgef\"uge multiprofessioneller Zusammenarbeit; Autonomie und Kooperation als zirkul\"are Aspekte; vier Berufsfelder (sonderp\"adagogische F\"orderung, Schulsozialarbeit, DaZ, Logop\"adie). Theoriebez\"uge: Werning/L\"oser 2010, Fussangel/Gr\"asel 2010/2011. Frage 5 zentrale Quelle.</t>
+          <t>Frage 5 Kernliteratur: S. 14–15 und S. 38–39 (4 S.). Kultursensible Elternarbeit, Perspektivumkehr und professionell begleitetes Dolmetschgespräch.</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -4468,550 +4452,75 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>gauckreimann2021psychdiagnostik</t>
+          <t>baudson2025besserfinden</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>244--247</t>
+          <t>35--40</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Gauck, Letizia; Reimann, Giselle</t>
+          <t>Baudson, Tanja Gabriele</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+          <t>Pauly, Claudia</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Psychologische Diagnostik in der Begabungs- und Begabtenförderung</t>
+          <t>Wie wir Begabte besser finden können</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Handbuch Begabung</t>
+          <t>Was ist fair? Begabungsgerechtigkeit auf dem Prüfstand</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>239–251</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr"/>
+          <t>35–40</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>10.25656/01:33972</t>
+        </is>
+      </c>
       <c r="P51" s="2" t="inlineStr"/>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>ca. 13 S. Vier-Schritte-Prozess; Deckeneffekt; Aisha-/Lea-Vignetten (deutschsprachiger Fallbeleg für Unteridentifikation).</t>
+          <t>6 S. (S. 35–40). Frage 5 Kernliteratur; Frage 1 Stützliteratur, nicht gezählt. Lehrkrafturteil: Underachiever, 2e-Lernende und Kinder mit Sprachbarrieren fallen aus dem Wahrnehmungsraster. Abgrenzung zu baudson2021wasdenken (Kernkorpus). Verifiziert via pdf\_extract.py. Open Access via pedocs.</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Frage 5 (BW, ZB/PV: Profession)</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Kernliteratur</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>kosoroklabhart2021voneltern</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>14--15, 38--39</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Košorok Labhart, Carmen; Schöllhorn, Angelika; Luginbühl, Dora</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>Von Eltern mit Migrationshintergrund lernen: Denkanstösse für die kultursensible Praxis in Spielgruppe, Kita und Schule</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>Ausgewählte Kapitel zur kultursensiblen Elternarbeit: 8 S. (Frage 5 im 500-S.-Korpus).</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Frage 5 (BW, ZB/PV: Profession)</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>gezaehlte Stuetzliteratur</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>muelleroppliger2021adaptive</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>384--387</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>Adaptive Lernarchitekturen: Begabungs- und Begabtenförderung innerhalb der Lerngemeinschaft</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch Begabung</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>374–389</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>16 S. (S. 374–389). Teil V \enquoteBegabender Unterricht. Definition adaptiver Lernarchitektur als Anpassung der Wissensvermittlung an Wissensstand, Lernpräferenzen und Möglichkeiten der Lernenden (S. 374\psq); empirische Wirksamkeit über alle ethnischen und sozioökonomischen Gruppen, Walberg-Metaanalyse 38 Studien/7200 Lernende (S. 375\psq); Ermöglichungsdidaktik nach Arnold/Schön 2019 (S. 377); vier konstituierende Merkmale (S. 378\psq); Hochbegabung weit mehr als fachliche Exzellenz, vier Bildungsdimensionen Begabung+soziales Kapital/Leadership/Verantwortung/Ethik (S. 380\psq); Lernberatung nach Shulman 2006 mit Knowing What/How/Why (S. 386\psq); erweiterte Leistungsbeurteilung mit Portfolio/Logbuch/Lernjournal (S. 387\psq); Schluss \enquoteanders als die anderen löst sich auf, denn alle sind anders (S. 388\psq). Achtung: Im PDF-Dateinamen und in einer früheren Manuskript-Version fälschlich als \enquoteS. 274–285 bzw. \enquoteS. 274–385 annotiert; auf S. 274–303 steht im Sammelband Preckels TAD-Beitrag.</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Frage 5 (BW, ZB/PV: Profession)</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>gezaehlte Stuetzliteratur</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>muelleroppliger2021plurale</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>40--42</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>Plurale Gesellschaft, Inklusion und Bildungsgerechtigkeit</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch Begabung</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>32–45</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>14 S. (S. 32–45). Frage 4 im 500-S.-Korpus.</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Frage 5 (BW, ZB/PV: Profession)</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>gezaehlte Stuetzliteratur</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>kummerwyss2017kooperativunterrichten</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>157, 160</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Kummer Wyss, Annemarie</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>Kooperativ unterrichten</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>Alle gleich – alle unterschiedlich! Zum Umgang mit Heterogenität in Schule und Unterricht</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>151–160</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="inlineStr"/>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>10 S. (S. 151–160). 3. Aufl. 2017 (Erstauflage 2010, S. 151–162 bei Klett und Balmer Zug). Beitrag im Sammelband Buholzer/Kummer Wyss; verbindet sich thematisch mit kappus2010migration (S. 63–77) und grossrieder2010anerkennung (S. 87–95) aus demselben Band. Volltext-PDF in Literatur/kummerwyss2017kooperativunterrichten/source.pdf.</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Frage 5 (BW, ZB/PV: Profession)</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>gezaehlte Stuetzliteratur</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>sedmak2021bildungsgerechtigkeit</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>71--72</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Sedmak, Clemens; Kapferer, Elisabeth</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Begabtenförderung und Bildungsgerechtigkeit</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch Begabung</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>65–76</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>12 S. (S. 65–76). Frage 4 im 500-S.-Korpus.</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Frage 5 (BW, ZB/PV: Profession)</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>gezaehlte Stuetzliteratur</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>wagener2021bfhemmendfoerdernd</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>424--425</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Wagener, Gundula</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>Begabungsfördernde und hemmende Wirkungsmechanismen im Klassenkontext</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>Handbuch Begabung</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>418–426</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>9 S. (S. 418–426). Teil V \enquoteBegabender Unterricht. Systemtheoretischer Rahmen mit Aktiotop und ökologischem Begabungsmodell (S. 418\psq); \enquoteDie Klasse macht den Unterschied (Schweitz 2003, S. 420); Bildungskapital-Typologie nach Ziegler/Stöger 2013 mit fünf Kategorien (S. 420\psq); Zimmer/Toma 2003 und Opdenakker/Van Damme 2001 zu sozioökonomisch differenzierten Effekten (S. 421); Peer-Mechanismen Big-Fish-Little-Pond, Acting White, Signaltheorie, Ansteckungstheorie (S. 421\psq) – relevant für begabte Migrantenkinder zwischen Peer-Kulturen; Pygmalion-Effekt auf Klassenebene (S. 423\psq); mehrstufige Zuständigkeitsaussage Lehrperson/Schulleitung/Bildungspolitik (S. 425); Quality Teaching als Effective+Good Teaching (Berliner 2005, S. 425\psq).</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R57"/>
+  <autoFilter ref="A1:R51"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5023,25 +4532,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
     <col width="55" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
   </cols>
@@ -5141,12 +4650,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Frage 4 (BW, DG/PV: Setting)</t>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5166,12 +4675,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>cast2024udlguidelines</t>
+          <t>baudson2021wasdenken</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>115--128</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -5179,48 +4688,56 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>CAST, Inc.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+          <t>Baudson, Tanja Gabriele</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Universal Design for Learning Guidelines</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Was Menschen über (Hoch-)Begabung und (Hoch-)Begabte denken: Individuelle und soziokulturelle Perspektiven</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>115–129</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>http://udlguidelines.cast.org</t>
-        </is>
-      </c>
+      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Version 3.0 (2024). UDL-Framework drei Hauptbereiche: Lernengagement (Interesse, Anstrengung, emotionale Kompetenz), Darstellung von Informationen (Wahrnehmung, Sprache, Wissensaufbau), Informationsverarbeitung und Ergebnisdarstellung (Zugang, Ausdruck, Strategieentwicklung). Frage 4- und Frage 5-relevant.</t>
+          <t>15 S. Gesamtumfang; Frage 3 zählt S. 115–129 (15 S.); Frage 1 und Frage 4 Stützliteratur, nicht gezählt. Seitenspanne von Inti verifiziert (KERNLITERATUR\_INTI.md, Fragen 1, 3, 5); der Scan umfasst die Fliesstext-Seiten 115–128 plus die erste Literaturseite 129. Volltext via OCR (source.pdf, komprimiert 6.7 MB) vorliegend. Gliederung: (1) Begriffliche Abgrenzungen, (2) Erkennen mit IQ-Kritik und Lehrkrafturteil ($\rho = .50$), (3) Hochbegabungs- konzeptionen (Disharmonie-Stereotyp, Cultural Mismatch, Minoritätenstress, Cass-Stufenmodell), (4) Folgerungen für globalisierte Gesellschaft. Schlüsselbeleg für FW1 (Sprache als Identifikationsbarriere, S. 120), FW3 (kultursensible Begabungsdiagnostik, S. 125) und BW4 (Inklusionsdebatte vergisst Begabung, S. 119). Vollständige verified\_quotes.md Status 4 vorliegend.</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Frage 4 (BW, DG/PV: Setting)</t>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5240,12 +4757,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>booth2019index</t>
+          <t>muelleroppliger2021begabungsmodelle</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>bei Frage 3 gezaehlt</t>
+          <t>204--219</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -5253,43 +4770,2704 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Booth, Tony; Ainscow, Mel</t>
+          <t>Müller-Oppliger, Victor</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Achermann, Bruno; Amirpur, Donja; Braunsteiner, Maria-Luise; Demo, Heidrun; Plate, Elisabeth; Platte, Andrea</t>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Index für Inklusion: Ein Leitfaden für Schulentwicklung</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Begabungsmodelle: Entwicklungslinien und Positionen zur Erfassung des Phänomens der Hochbegabung</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>204–222</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Dimensionen A–C: ca. 90 S. (verteilt auf Fr. 3 und 4)</t>
+          <t>16 S. (S. 204–219, ohne Literaturverzeichnis). Frage 4 Kernliteratur; Frage 1 Stützliteratur, nicht gezählt. Dynamisch- mehrdimensionale Begabungsmodelle: Renzulli (Drei-Ringe), Mönks (Triadisches Interdependenzmodell), Münchner Hochbegabungsmodell (Heller/Perleth), Aktiotop (Ziegler), DMGT (Gagné). Begabung als entwicklungsoffenes Potenzial; Differenzierung Potenzial/Performanz.</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>muelleroppliger2021paeddiagnostik</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>224--235</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Salomé</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Pädagogische Diagnostik: Potenzialerfassung und Förderdiagnostik</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>224–238</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>15 S. Gesamtumfang; Frage 4 zählt S. 224–235 (12 S.); Frage 1 und Frage 5 Stützliteratur, nicht gezählt. Phasenmodell vermuten/wahrnehmen/erkennen; Meeraugenprinzip; Förder- vs. Statusdiagnostik.</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>baudson2025besserfinden</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35--40</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Baudson, Tanja Gabriele</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Pauly, Claudia</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Wie wir Begabte besser finden können</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Was ist fair? Begabungsgerechtigkeit auf dem Prüfstand</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>35–40</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>10.25656/01:33972</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>6 S. (S. 35–40). Frage 5 Kernliteratur; Frage 1 Stützliteratur, nicht gezählt. Lehrkrafturteil: Underachiever, 2e-Lernende und Kinder mit Sprachbarrieren fallen aus dem Wahrnehmungsraster. Abgrenzung zu baudson2021wasdenken (Kernkorpus). Verifiziert via pdf\_extract.py. Open Access via pedocs.</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>trautmann2016einfuehrung</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>34--41</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Trautmann, Thomas</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Einführung in die Hochbegabtenpädagogik</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Lokal verfügbarer Foto-Auszug (komprimiert): Kap. zu Multiplen Intelligenzen nach Gardner, S. 34–41 (8 S.) – siehe Literatur/trautmann2016einfuehrung/kap\_multiple\_intelligenzen\_s034-041.pdf. Im Lerndokument als Beleg für Gardners Theorie zitiert (FW1, Begabungsmodelle als deutschsprachige Standardeinführung).</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>hoyer2013begabung</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73--74</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Hoyer, Timo; Weigand, Gabriele; Müller-Oppliger, Victor</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Begabung: Eine Einführung</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Vorgaenger-/Schwesterpublikation zu Handbuch Begabung 2021. Frage 4 zählt S. 94–99 (6 S.). Kap. 5.1 Konzepte/Modelle (Gardner, Multiple Intelligenzen); Kap. 6.6 Turning Point: Das ``Three Ring Concept''; Kap. 7.1 Das ``Schoolwide Enrichment Model'' als Choreografie inklusiver Begabungs- und Begabtenfoerderung.</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>lehwald2017motivation</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>78--92</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Lehwald, Gerhard</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Motivation trifft Begabung: Begabte Kinder und Jugendliche verstehen und gezielt fördern</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Kernreferenzen: (a) S. 57–63 = Fall Pawel, hochbegabter Underachiever, Frage 3 Stützliteratur, nicht gezählt; (b) S. 70–72 = Sechsstufige Stufenfolge ins Underachievement (Abb. 2-5); (c) S. 84–89 = Flow als empirisch st\"arkster Begabungspr\"adiktor; (d) S. 151–158 = F\"orderlogik (Differenzierung, Compacting, Enrichment, Akzeleration), Frage 4 Kernliteratur. Bewusst nicht im Korpus: HST-P/FES/BVE (S. 107–134) wegen Sprachbarriere bei S.; Triadisches Modell (S. 65–69) wegen Redundanz.</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>kappus2010migration</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>63--70, 74</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Kappus, Elke-Nicole</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Umgang mit migrationsbedingter Heterogenität</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Alle gleich – alle unterschiedlich: Zum Umgang mit Heterogenität in Schule und Unterricht</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>63–77</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>15 S. Gesamtumfang; Frage 1 und Frage 3 Stützliteratur, nicht gezählt. Frage 3 verweist auf S. 63–70, 74. Volltext (Foto-Scan, komprimiert) liegt vor unter Literatur/kappus2010migration/source.pdf (5,0 MB). Inhaltsverzeichnis- Position bestätigt via Buholzer-Sammelband (Universitätsbibliothek Basel, IDSBB 005018146): Kappus-Beitrag steht in Teil I \enquoteErscheinungsweisen von Heterogenität.</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>grossenbacher2014integrative</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>317--325</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Grossenbacher, Silvia; Tettenborn, Annette</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Stamm, Margrit</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Talent und Begabung in der Volksschule der deutschsprachigen Schweiz</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Talententwicklung: Theorien, Methoden und Praxis in Psychologie und Pädagogik</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>317–325</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4 Kernliteratur: S. 317–325 (9 S.). Schweizer Volksschulkontext, integrative Begabungs- und Begabtenf\"orderung als Auftrag der Volksschule, Massnahmenrepertoire (Differenzierung, Compacting, Enrichment, Akzeleration, Pullout, regionale Angebote), Kooperation Regelunterricht und Heilp\"adagogik, Schulentwicklung. Aus demselben Sammelband: \citestamm2014handbuch. Verifiziert via DNB (idn=1045975508) und lokaler Foto-Scan.</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>erzinger2023pisa</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45--48</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Erzinger, Andrea B.; Pham, Giang; Prosperi, Oliver; Salvisberg, Miriam</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>PISA 2022: Die Schweiz im Fokus</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.admin.ch/gov/de/start/dokumentation/medienmitteilungen.msg-id-99216.html</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>bfs2022migration</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>34--35</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Bundesamt für Statistik BFS</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Migration und Integration: Migrationsbewegungen und Bevölkerung mit Migrationshintergrund</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>dvs2025bbf</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Dienststelle Volksschulbildung Luzern</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Integrative Begabungs- und Begabtenförderung</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>https://volksschulbildung.lu.ch/unterricht_organisation/uo_foerderangebote/uo_fa_begabungsfoerderung</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 und Frage 4 Stützliteratur, nicht gezählt. Kantonale Umsetzungshilfe zur integrativen Begabungs- und Begabtenförderung.</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 (FW, KS/DG: Erkennen)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>maehler2018diagnostik</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Kap. 1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Maehler, Débora B.; Shajek, Alexandra; Brinkmann, Heinz Ulrich</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Diagnostik bei Migrantinnen und Migranten: Ein Handbuch</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Kap. 1 Einleitung (drei Fehlerquellen sprachlicher Verständnisschwierigkeiten, kulturell unterschiedlicher Testvertrautheit, migrationsspezifischer Stressoren): 12 S. Im 500-S.-Kernkorpus für Frage 1.</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Frage 2 (FW, MW/KS: Barrieren)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>baumschader2021twice</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>588--598</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Baum, Susan; Schader, Robin</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>\enquoteTwice Exceptionality – in zweifacher Hinsicht aussergewöhnlich: Geschichte, Charakteristika und Möglichkeiten erfolgreichen Lernens</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>588–600</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>13 S. Gesamtumfang; Frage 1 zählt S. 588–598 (11 S.); Frage 2 und Frage 3 Stützliteratur, nicht gezählt. Schlussbeitrag im Teil VIII \enquoteDysfunktionale Begabungsentwicklung des Handbuchs Begabung. Historische Entwicklung des 2e-Konzepts, Charakteristika und Lernbedingungen. Volltext verfügbar via teil8\_dysfunktionale\_begabungsentwicklung.md in baumschader2021twice/.</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Frage 2 (FW, MW/KS: Barrieren)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>warneckehauke2020bildungsgerechtigkeit</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>247--252</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Warnecke, Sabine; Hauke, Robert</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Fischer, Christian; Fischer-Ontrup, Christiane; Käpnick, Friedhelm; Neuber, Nils; Solzbacher, Claudia; Zwitserlood, Pienie</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Stärkung der Bildungsgerechtigkeit bei Underachievement, Migration und Hochbegabung: Drei Beispiele aus der Förderpraxis</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Begabungsförderung, Leistungsentwicklung, Bildungsgerechtigkeit – für alle! II. Beiträge aus der Begabungsförderung</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>241–252</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>12 S. (S. 241–252). Frage 1 zählt S. 241–252; Frage 2 Stützliteratur S. 247–252, nicht gezählt. Praxis- und Gerechtigkeitsbezug. Drei Beispiele aus der Förderpraxis: Underachievement, Migration und Hochbegabung gemeinsam adressiert. Beziehung, Geduld, positive Verstärkung, Offenheit für individuelle Unterschiede, Passung zu besonderen Interessen. Cited content: S. 247–252.</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Frage 2 (FW, MW/KS: Barrieren)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>hoyer2013begabung</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>111--113</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Hoyer, Timo; Weigand, Gabriele; Müller-Oppliger, Victor</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Begabung: Eine Einführung</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Vorgaenger-/Schwesterpublikation zu Handbuch Begabung 2021. Frage 4 zählt S. 94–99 (6 S.). Kap. 5.1 Konzepte/Modelle (Gardner, Multiple Intelligenzen); Kap. 6.6 Turning Point: Das ``Three Ring Concept''; Kap. 7.1 Das ``Schoolwide Enrichment Model'' als Choreografie inklusiver Begabungs- und Begabtenfoerderung.</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Frage 2 (FW, MW/KS: Barrieren)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>sturm2016graphomotorik</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>183--198</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Sturm, Afra</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Liebers, Katrin; Landwehr, Brunhild; Reinhold, Simone; Riegler, Susanne; Schmidt, Romina</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Zur Bedeutung der graphomotorischen Prozesse beim Schreiben(lernen)</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Facetten grundschulpädagogischer und -didaktischer Forschung</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>183–198</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>16 S. (S. 183–198). Frage 2 Stützliteratur, nicht gezählt.</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Frage 3 (FW, PB: Beziehung)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>baumschader2021twice</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>588--598</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Baum, Susan; Schader, Robin</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>\enquoteTwice Exceptionality – in zweifacher Hinsicht aussergewöhnlich: Geschichte, Charakteristika und Möglichkeiten erfolgreichen Lernens</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>588–600</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>13 S. Gesamtumfang; Frage 1 zählt S. 588–598 (11 S.); Frage 2 und Frage 3 Stützliteratur, nicht gezählt. Schlussbeitrag im Teil VIII \enquoteDysfunktionale Begabungsentwicklung des Handbuchs Begabung. Historische Entwicklung des 2e-Konzepts, Charakteristika und Lernbedingungen. Volltext verfügbar via teil8\_dysfunktionale\_begabungsentwicklung.md in baumschader2021twice/.</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Frage 3 (FW, PB: Beziehung)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>kappus2010migration</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>63--70, 74</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Kappus, Elke-Nicole</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Umgang mit migrationsbedingter Heterogenität</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Alle gleich – alle unterschiedlich: Zum Umgang mit Heterogenität in Schule und Unterricht</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>63–77</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>15 S. Gesamtumfang; Frage 1 und Frage 3 Stützliteratur, nicht gezählt. Frage 3 verweist auf S. 63–70, 74. Volltext (Foto-Scan, komprimiert) liegt vor unter Literatur/kappus2010migration/source.pdf (5,0 MB). Inhaltsverzeichnis- Position bestätigt via Buholzer-Sammelband (Universitätsbibliothek Basel, IDSBB 005018146): Kappus-Beitrag steht in Teil I \enquoteErscheinungsweisen von Heterogenität.</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Frage 3 (FW, PB: Beziehung)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>baumert2022freundschaftwerte</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>40--49</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Baumert, Britta</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>\enquoteMan kann nicht leben, wenn man keine Freunde hat: Wertezuschreibungen Jugendlicher mit und ohne Fluchterfahrung im Themenbereich Freundschaft</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>36–50</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>10.11576/pflb-5878</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>15 S. Gesamtumfang; Frage 3 Stützliteratur, nicht gezählt, S. 40–49. Empirische Studie zu Freundschaftswerten bei Jugendlichen mit/ohne Fluchterfahrung. verified\_quotes.md vorliegend (Status 4).</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Frage 3 (FW, PB: Beziehung)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>gysinscherzinger2022freundschaftenwertvoll</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8--12</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Gysin, Stefanie; Scherzinger, Marion</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Freundschaften machen das Leben wertvoll</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>8–12</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>5 S. (S. 8–12). Frage 3 Stützliteratur, nicht gezählt. Schweizer Beitrag zur Bedeutung von Freundschaften für Wohlbefinden. Volltext-Auszug in Literatur/gysinscherzinger2022freundschaftenwertvoll/source.pdf (Seiten 8–12 aus dem Heft extrahiert).</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Frage 3 (FW, PB: Beziehung)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>evers2025stress</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>21--27</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Evers, Wiebke</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Pauly, Claudia</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Stress als Dämpfer für die kognitive Entwicklung und die Entfaltung von Begabung</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Was ist fair? Begabungsgerechtigkeit auf dem Prüfstand</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>21–27</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>10.25656/01:33972</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>7 S. (S. 21–27). Frage 3 Stützliteratur, nicht gezählt. Dauerstress beeintr\"achtigt Lernen, Selbstregulation, Ged\"achtnis und Probleml\"osen. Verifiziert via pdf\_extract.py. Open Access via pedocs.</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Frage 3 (FW, PB: Beziehung)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>lehwald2017motivation</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>57--63</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Lehwald, Gerhard</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Motivation trifft Begabung: Begabte Kinder und Jugendliche verstehen und gezielt fördern</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Kernreferenzen: (a) S. 57–63 = Fall Pawel, hochbegabter Underachiever, Frage 3 Stützliteratur, nicht gezählt; (b) S. 70–72 = Sechsstufige Stufenfolge ins Underachievement (Abb. 2-5); (c) S. 84–89 = Flow als empirisch st\"arkster Begabungspr\"adiktor; (d) S. 151–158 = F\"orderlogik (Differenzierung, Compacting, Enrichment, Akzeleration), Frage 4 Kernliteratur. Bewusst nicht im Korpus: HST-P/FES/BVE (S. 107–134) wegen Sprachbarriere bei S.; Triadisches Modell (S. 65–69) wegen Redundanz.</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4 (BW, DG/PV: Setting)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>horvath2021elite</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>77--87</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Horvath, Kenneth</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Elite, Begabung und soziale Ungleichheit: Ungelöste Gerechtigkeitsfragen</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>77–87</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 Kernliteratur: S. 77–87 (11 S.); Frage 4 Stützliteratur, nicht gezählt. Von Inti verifiziert (KERNLITERATUR\_INTI.md, Fragen 1, 4, 5). Meritokratische Illusion, Pygmalion-Effekt, Migrationshintergrund als verwobene Kategorie.</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4 (BW, DG/PV: Setting)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>weigand2021person</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>46--59</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Begabung, Bildung und Person</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>46–63</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>18 S. Gesamtumfang; Frage 5 zählt S. 46–59 (14 S.); Frage 4 Stützliteratur, nicht gezählt. Philosophisch-pädagogisches Fundament: konstitutive, kritisch-konstruktive und regulative Funktion des Personenprinzips.</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4 (BW, DG/PV: Setting)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>baudson2021wasdenken</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Baudson, Tanja Gabriele</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Was Menschen über (Hoch-)Begabung und (Hoch-)Begabte denken: Individuelle und soziokulturelle Perspektiven</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>115–129</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>15 S. Gesamtumfang; Frage 3 zählt S. 115–129 (15 S.); Frage 1 und Frage 4 Stützliteratur, nicht gezählt. Seitenspanne von Inti verifiziert (KERNLITERATUR\_INTI.md, Fragen 1, 3, 5); der Scan umfasst die Fliesstext-Seiten 115–128 plus die erste Literaturseite 129. Volltext via OCR (source.pdf, komprimiert 6.7 MB) vorliegend. Gliederung: (1) Begriffliche Abgrenzungen, (2) Erkennen mit IQ-Kritik und Lehrkrafturteil ($\rho = .50$), (3) Hochbegabungs- konzeptionen (Disharmonie-Stereotyp, Cultural Mismatch, Minoritätenstress, Cass-Stufenmodell), (4) Folgerungen für globalisierte Gesellschaft. Schlüsselbeleg für FW1 (Sprache als Identifikationsbarriere, S. 120), FW3 (kultursensible Begabungsdiagnostik, S. 125) und BW4 (Inklusionsdebatte vergisst Begabung, S. 119). Vollständige verified\_quotes.md Status 4 vorliegend.</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4 (BW, DG/PV: Setting)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>dvs2025bbf</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Dienststelle Volksschulbildung Luzern</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Integrative Begabungs- und Begabtenförderung</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>https://volksschulbildung.lu.ch/unterricht_organisation/uo_foerderangebote/uo_fa_begabungsfoerderung</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Frage 1 und Frage 4 Stützliteratur, nicht gezählt. Kantonale Umsetzungshilfe zur integrativen Begabungs- und Begabtenförderung.</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4 (BW, DG/PV: Setting)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>leikhof2021jugendliche</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Kap. 1--2</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Leikhof, Ulrike</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Jugendliche mit Migrationshintergrund in der Begabungsförderung – eine Bestandsaufnahme</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Kap. 1–2 (Bestandsaufnahme, Erwartungseffekte): Frage 4 Stützliteratur, nicht gezählt.</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 (BW, ZB/PV: Profession)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>muelleroppliger2021paeddiagnostik</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>224--238</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Salomé</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Pädagogische Diagnostik: Potenzialerfassung und Förderdiagnostik</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>224–238</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>15 S. Gesamtumfang; Frage 4 zählt S. 224–235 (12 S.); Frage 1 und Frage 5 Stützliteratur, nicht gezählt. Phasenmodell vermuten/wahrnehmen/erkennen; Meeraugenprinzip; Förder- vs. Statusdiagnostik.</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 (BW, ZB/PV: Profession)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>reisrenzullimueller2021sem</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>333--347</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Reis, Sally M.; Renzulli, Joseph S.; Müller-Oppliger, Victor</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Das Schoolwide Enrichment Model (SEM): Vier Jahrzehnte Forschung zur Entwicklung von Talenten und kreativer Produktivität</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>333–347</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>15 S. Gesamtumfang; Frage 4 zählt S. 333–345 (13 S.); Frage 5 Stützliteratur, nicht gezählt. SEM-Hauptbeitrag im Handbuch Begabung, Teil IV \enquoteBegabende Schule. Drei-Ringe-Konzept als anti-essenzialistische Basis (S. 334\psq); RIS mit alternativen Identifikationspfaden für die 50 % nicht durch Standardtests Erkannten (S. 337); Enrichment Triad mit Typ I/II/III (S. 338\psq); Drehtürmodell (S. 342) und Schlüsselsatz \enquoteBegabung ist kein schulpsychologischer Fall; Curriculum Compacting (S. 343\psq); Schweizer SEM-Praxis an PH FHNW seit 2003 (S. 344\psq); Längsschnittstudien Delcourt 1993, Hébert 1993, Westberg, Renzulli/Reis 2014 (S. 346\psq). Achtung: Im bisherigen Manuskript fälschlich unter dem Citekey \textttrenzullireis2021rls zitiert – jener verweist auf den anderen Beitrag der beiden Autor:innen zum \enquoteRenzulli-Lernsystem (S. 444–454).</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 (BW, ZB/PV: Profession)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>weigand2021separativ</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>290--298</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Weigand, Gabriele; Kaiser, Michaela</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Separativ oder integrativ? Inklusive Begabungs- und Begabtenförderung</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>290–298</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>9 S. (S. 290–298). Frage 4 Kernliteratur; Frage 5 Stützliteratur, nicht gezählt. Cheflektorat 2026-05-01: Seitenangabe von zuvor 290–301 auf 290–298 korrigiert (Originalumfang des argumentativen Kapitelteils; das Folgekapitel Anderegg/Wilhelm beginnt im Sammelband nach S. 298).</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 (BW, ZB/PV: Profession)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>muelleroppliger2021plurale</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>32--45</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Plurale Gesellschaft, Inklusion und Bildungsgerechtigkeit</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>32–45</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>14 S. Gesamtumfang; Frage 4 zählt S. 32–42 (11 S.); Frage 5 Stützliteratur S. 32–45, nicht gezählt.</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 (BW, ZB/PV: Profession)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>sedmak2021bildungsgerechtigkeit</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>65--75</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Sedmak, Clemens; Kapferer, Elisabeth</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Begabtenförderung und Bildungsgerechtigkeit</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>65–76</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>12 S. Gesamtumfang; Frage 4 zählt S. 65–75 (11 S.); Frage 5 Stützliteratur S. 65–75, nicht gezählt.</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 (BW, ZB/PV: Profession)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>muelleroppliger2021adaptive</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>384--385</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Adaptive Lernarchitekturen: Begabungs- und Begabtenförderung innerhalb der Lerngemeinschaft</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>374–389</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>16 S. Gesamtumfang; Frage 4 zählt S. 374–385 (12 S.); Frage 5 Stützliteratur S. 384–385, nicht gezählt. Teil V \enquoteBegabender Unterricht. Definition adaptiver Lernarchitektur als Anpassung der Wissensvermittlung an Wissensstand, Lernpräferenzen und Möglichkeiten der Lernenden (S. 374\psq); empirische Wirksamkeit über alle ethnischen und sozioökonomischen Gruppen, Walberg-Metaanalyse 38 Studien/7200 Lernende (S. 375\psq); Ermöglichungsdidaktik nach Arnold/Schön 2019 (S. 377); vier konstituierende Merkmale (S. 378\psq); Hochbegabung weit mehr als fachliche Exzellenz, vier Bildungsdimensionen Begabung+soziales Kapital/Leadership/Verantwortung/Ethik (S. 380\psq); Lernberatung nach Shulman 2006 mit Knowing What/How/Why (S. 386\psq); erweiterte Leistungsbeurteilung mit Portfolio/Logbuch/Lernjournal (S. 387\psq); Schluss \enquoteanders als die anderen löst sich auf, denn alle sind anders (S. 388\psq). Achtung: Im PDF-Dateinamen und in einer früheren Manuskript-Version fälschlich als \enquoteS. 274–285 bzw. \enquoteS. 274–385 annotiert; auf S. 274–303 steht im Sammelband Preckels TAD-Beitrag.</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 (BW, ZB/PV: Profession)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>wagener2021bfhemmendfoerdernd</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>418--424</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Wagener, Gundula</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oppliger, Victor; Weigand, Gabriele</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Begabungsfördernde und hemmende Wirkungsmechanismen im Klassenkontext</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Handbuch Begabung</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>418–426</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>9 S. Gesamtumfang; Frage 3 zählt S. 418–424 (7 S.); Frage 5 Stützliteratur S. 418–424, nicht gezählt. Teil V \enquoteBegabender Unterricht. Systemtheoretischer Rahmen mit Aktiotop und ökologischem Begabungsmodell (S. 418\psq); \enquoteDie Klasse macht den Unterschied (Schweitz 2003, S. 420); Bildungskapital-Typologie nach Ziegler/Stöger 2013 mit fünf Kategorien (S. 420\psq); Zimmer/Toma 2003 und Opdenakker/Van Damme 2001 zu sozioökonomisch differenzierten Effekten (S. 421); Peer-Mechanismen Big-Fish-Little-Pond, Acting White, Signaltheorie, Ansteckungstheorie (S. 421\psq) – relevant für begabte Migrantenkinder zwischen Peer-Kulturen; Pygmalion-Effekt auf Klassenebene (S. 423\psq); mehrstufige Zuständigkeitsaussage Lehrperson/Schulleitung/Bildungspolitik (S. 425); Quality Teaching als Effective+Good Teaching (Berliner 2005, S. 425\psq).</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Frage 5 (BW, ZB/PV: Profession)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>nicht gezaehlt</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>kummerwyss2017kooperativunterrichten</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>151--154, 156--160</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Kummer Wyss, Annemarie</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Buholzer, Alois; Kummer Wyss, Annemarie</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Kooperativ unterrichten</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Alle gleich – alle unterschiedlich! Zum Umgang mit Heterogenität in Schule und Unterricht</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>151–160</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>10 S. (S. 151–160). 3. Aufl. 2017 (Erstauflage 2010, S. 151–162 bei Klett und Balmer Zug). Beitrag im Sammelband Buholzer/Kummer Wyss; verbindet sich thematisch mit kappus2010migration (S. 63–77) und grossrieder2010anerkennung (S. 87–95) aus demselben Band. Frage 5 Stützliteratur: S. 151–154 und S. 156–160, nicht gezählt. Volltext-PDF in Literatur/kummerwyss2017kooperativunterrichten/source.pdf.</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R3"/>
+  <autoFilter ref="A1:R37"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5333,7 +7511,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -5348,7 +7526,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -5363,7 +7541,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -5378,7 +7556,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -5393,7 +7571,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -5408,7 +7586,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
     </row>
@@ -5451,7 +7629,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1ea2a3b7982894bf40cfb340509f8c4eb798c4bfa839236139564c220df0fe09</t>
+          <t>0e7bae4a7f5b356c121a36aec9e6b5d67f57a176f96d22cf049a6703c105d431</t>
         </is>
       </c>
     </row>
@@ -5487,7 +7665,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-01T13:21:58+00:00</t>
+          <t>2026-05-01T15:59:06+00:00</t>
         </is>
       </c>
     </row>
